--- a/02_screening/022_Anomalies/momentum.xlsx
+++ b/02_screening/022_Anomalies/momentum.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zlhte\OneDrive\Desktop\X\02_screening\022_Anomalies\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BD692B6-E757-47EF-A955-F98355DE2BD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BF3E801-C991-4B12-B762-DA2AA3758FBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" firstSheet="1" activeTab="3" xr2:uid="{E8E2FE8C-4884-4018-8A72-37146AA5AB4B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="4" xr2:uid="{E8E2FE8C-4884-4018-8A72-37146AA5AB4B}"/>
   </bookViews>
   <sheets>
     <sheet name="__snloffice" sheetId="3" state="veryHidden" r:id="rId1"/>
@@ -3560,7 +3560,7 @@
     <t>䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䕁䅷杗歁䑁䅅䅏䅁䅁䩕䅁㑂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊䵂䙁䅯䅊㕁䅁䅁兤䅣䡁䅧䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䕁䄰䅊硁䑁䅅䅁㙄睁䅁䅥䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑兔歁䑁䅅䅏䅁䭁䡯䅁㉂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊乂䍁䅑兏䅁偁䑳䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊乂䕁䅅䅊硁䑁䅅䅁㉂睂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑兔䉂䍁䅑免㑁䅁䅁杂䅫䡁䅧䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䕁䄰兑歁䑁䅫䅁㍂睂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑兔䍂䍁䅑免硁䅁䅁睥䅣䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䕁䄰村歁䑁䅅䅏䅁䍁䕧䅁㑂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊乂䕁䅉䅊㕁䅁䅁克䅑䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䕁䄰睑歁䑁䅅免䅁䕁䡅䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊乂䕁䅍䅊硁䑁䅧䅁权兂䅁䅥䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑兔䑂䍁䅑兏䅁䭁䙅䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊乂䕁䅑䅊硁䑁䅅䅁卂䅂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑兔䕂䍁䅑免㑁䅁䅁䅐䅧䡁䅧䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䕁䄰䅒歁䑁䅫䅁呂䅂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑兔䙂䍁䅑免硁䅁䅁䅱䅍䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䕁䄰兒歁䑁䅅䅏䅁䅁䩣䅁㑂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊乂䕁䅕䅊㕁䅁䅁共䅍䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䕁䄰杒歁䑁䅅免䅁䱁䙣䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊乂䕁䅙䅊硁䑁䅧䅁啂䅃䅁䅥䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑兔䝂䍁䅑兏䅁䱁䙧䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊乂䕁䅣䅊硁䑁䅅䅁祂兂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑兔䡂䍁䅑免㑁䅁䅁䅰䅍䡁䅧䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䕁䄰睒歁䑁䅫䅁汃睁䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑兔䥂䍁䅑免硁䅁䅁睥䅍䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䕁䄰䅓歁䑁䅅䅏䅁偁䐴䅁㑂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊乂䕁䅧䅊㕁䅁䅁䅦䅍䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䕁䄰兓歁䑁䅅免䅁䵁䐴䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊乂䕁䅫䅊硁䑁䅧䅁癄兂䅁䅥䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑兔䩂䍁䅑兏䅁䵁䐸䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊乂䕁䅯䅊硁䑁䅅䅁䅃睂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑兔䭂䍁䅑免㑁䅁䅁䅃䅫䡁䅧䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䕁䄰杓歁䑁䅫䅁䉃睂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑兔䱂䍁䅑免硁䅁䅁杧䅣䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䕁䄰睓歁䑁䅅䅏䅁䅁䩫䅁㑂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊乂䕁䅳䅊㕁䅁䅁睧䅣䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䕁䄰䅔歁䑁䅅免䅁偁䔰䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊乂䕁䅷䅊硁䑁䅧䅁䭁元䅁䅥䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑兔䵂䍁䅑兏䅁偁䔴䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊乂䕁䄰䅊硁䑁䅅䅁橂杂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑兔乂䍁䅑免㑁䅁䅁䅄䅫䡁䅧䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䕁䄰兔歁䑁䅫䅁歂杂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑兔佂䍁䅑免硁䅁䅁李䅑䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䕁䄰杔歁䑁䅅䅏䅁䅁䨰䅁㑂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊乂䕁䄴䅊㕁䅁䅁睎䅑䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䕁䄰睔歁䑁䅅免䅁䕁䙁䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊乂䕁䄸䅊硁䑁䅧䅁求䅃䅁䅥䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑兔偂䍁䅑兏䅁䕁䙅䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊乂䙁䅁䅊硁䑁䅅䅁䝃睂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑兔兂䍁䅑免㑁䅁䅁䅦䅣䡁䅧䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䕁䄰䅕歁䑁䅫䅁㥂睂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑兔剂䍁䅑免硁䅁䅁兕䅣䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䕁䄰兕歁䑁䅅䅏䅁䅁䨴䅁㑂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊乂䙁䅅䅊㕁䅁䅁杕䅣䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䕁䄰杕歁䑁䅅免䅁䥁䡣䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊乂䙁䅉䅊硁䑁䅧䅁允元䅁䅥䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑兔卂䍁䅑兏䅁䥁䡧䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊乂䙁䅍䅊硁䑁䅅䅁䙂睂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑兔呂䍁䅑免㑁䅁䅁睅䅫䡁䅧䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䕁䄰睕歁䑁䅫䅁䝂睂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑兔啂䍁䅑免硁䅁䅁兡䅣䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䕁䄰䅖歁䑁䅅䅏䅁䵁䑑䅁㑂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊乂䙁䅑䅊㕁䅁䅁典䅍䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䕁䄰兖歁䑁䅅免䅁䵁䕣䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊乂䙁䅕䅊硁䑁䅧䅁㉄杂䅁䅥䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑兔噂䍁䅑兏䅁䵁䕧䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊乂䙁䅙䅊硁䑁䅅䅁捂睂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑兔坂䍁䅑免㑁䅁䅁杪䅍䡁䅧䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䕁䄰杖歁䑁䅫䅁偃睁䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑兔塂䍁䅑免硁䅁䅁䅙䅣䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䕁䄰睖歁䑁䅅䅏䅁䅁䥷䅁㑂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊乂䙁䅣䅊㕁䅁䅁兙䅣䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䕁䄰䅗歁䑁䅅免䅁䥁䡯䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊乂䙁䅧䅊硁䑁䅧䅁煄䅃䅁䅥䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑兔奂䍁䅑兏䅁䥁䡳䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊乂䙁䅫䅊硁䑁䅅䅁噄杂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑兔婂䍁䅑免㑁䅁䅁䅆䅫䡁䅧䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䕁䄰兗歁䑁䅫䅁坄杂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑兔慂䍁䅑免硁䅁䅁䅪䅣䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䕁䄰杗歁䑁䅅䅏䅁䉁䙯䅁㑂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊乂䙁䅯䅊㕁䅁䅁睇䅕䡁䅧䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䕁䄴䅊硁䑁䅅䅁䩁䅂䅁䅥䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑杔歁䑁䅅䅏䅁䍁䥷䅁㉂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊佂䍁䅑兏䅁䅁䕯䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊佂䕁䅅䅊硁䑁䅅䅁乃睂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑杔䉂䍁䅑免㑁䅁䅁䅫䅙䡁䅧䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䕁䄴兑歁䑁䅫䅁剃杂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑杔䍂䍁䅑免硁䅁䅁睪䅣䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䕁䄴村歁䑁䅅䅏䅁䉁䩙䅁㑂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊佂䕁䅉䅊㕁䅁䅁䅫䅣䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䕁䄴睑歁䑁䅅免䅁䡁䡫䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊佂䕁䅍䅊硁䑁䅧䅁塁元䅁䅥䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑杔䑂䍁䅑兏䅁䡁䡯䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊佂䕁䅑䅊硁䑁䅅䅁灄䅂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑杔䕂䍁䅑免㑁䅁䅁充䅫䡁䅧䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䕁䄴䅒歁䑁䅫䅁煄䅂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑杔䙂䍁䅑免硁䅁䅁杰䅕䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䕁䄴兒歁䑁䅅䅏䅁䕁䡁䅁㑂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊佂䕁䅕䅊㕁䅁䅁睰䅕䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䕁䄴杒歁䑁䅅免䅁乁䝷䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊佂䕁䅙䅊硁䑁䅧䅁奁元䅁䅥䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑杔䝂䍁䅑兏䅁乁䜰䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊佂䕁䅣䅊硁䑁䅅䅁剃睂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑杔䡂䍁䅑免㑁䅁䅁睄䅑䡁䅧䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䕁䄴睒歁䑁䅫䅁允䅂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑杔䥂䍁䅑免硁䅁䅁睬䅣䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䕁䄴䅓歁䑁䅅䅏䅁䍁䕍䅁㑂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊佂䕁䅧䅊㕁䅁䅁䅊䅑䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䕁䄴兓歁䑁䅅免䅁䩁䡧䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊佂䕁䅫䅊硁䑁䅧䅁婁元䅁䅥䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑杔䩂䍁䅑兏䅁䩁䡫䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊佂䕁䅯䅊硁䑁䅅䅁慃睂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑杔䭂䍁䅑免㑁䅁䅁䅦䅙䡁䅧䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䕁䄴杓歁䑁䅫䅁㥂杂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑杔䱂䍁䅑免硁䅁䅁朲䅍䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䕁䄴睓歁䑁䅅䅏䅁䥁䝫䅁㑂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊佂䕁䅳䅊㕁䅁䅁眲䅍䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䕁䄴䅔歁䑁䅅免䅁䕁䡯䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊佂䕁䅷䅊硁䑁䅧䅁祃䅃䅁䅥䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑杔䵂䍁䅑兏䅁䕁䡳䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊佂䕁䄰䅊硁䑁䅅䅁扃睂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑杔乂䍁䅑免㑁䅁䅁杇䅫䡁䅧䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䕁䄴兔歁䑁䅫䅁捃睂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑杔佂䍁䅑免硁䅁䅁睮䅣䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䕁䄴杔歁䑁䅅䅏䅁䵁䥫䅁㑂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊佂䕁䄴䅊㕁䅁䅁䅯䅣䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䕁䄴睔歁䑁䅅免䅁䭁䔰䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊佂䕁䄸䅊硁䑁䅧䅁元兂䅁䅥䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑杔偂䍁䅑兏䅁䭁䔴䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊佂䙁䅁䅊硁䑁䅅䅁桃睂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑杔兂䍁䅑免㑁䅁䅁杯䅕䡁䅧䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䕁䄴䅕歁䑁䅫䅁橃兂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑杔剂䍁䅑免硁䅁䅁睯䅣䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䕁䄴兕歁䑁䅅䅏䅁佁䤸䅁㑂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊佂䙁䅅䅊㕁䅁䅁䅰䅣䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䕁䄴杕歁䑁䅅免䅁䭁䡕䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊佂䙁䅉䅊硁䑁䅧䅁瑁䅃䅁䅥䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑杔卂䍁䅑兏䅁䭁䡙䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊佂䙁䅍䅊硁䑁䅅䅁煁杂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑杔呂䍁䅑免㑁䅁䅁兹䅙䡁䅧䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䕁䄴睕歁䑁䅫䅁牁杂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑杔啂䍁䅑免硁䅁䅁睰䅣䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䕁䄴䅖歁䑁䅅䅏䅁䅁䡅䅁㑂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊佂䙁䅑䅊㕁䅁䅁杁䅣䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䕁䄴兖歁䑁䅅免䅁偁䙧䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊佂䙁䅕䅊硁䑁䅧䅁扁元䅁䅥䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑杔噂䍁䅑兏䅁偁䙫䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊佂䙁䅙䅊硁䑁䅅䅁⽃杂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑杔坂䍁䅑免㑁䅁䅁杦䅣䡁䅧䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䕁䄴杖歁䑁䅫䅁䅄杂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑杔塂䍁䅑免硁䅁䅁睱䅣䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䕁䄴睖歁䑁䅅䅏䅁䡁䜴䅁㑂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊佂䙁䅣䅊㕁䅁䅁睦䅙䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䕁䄴䅗歁䑁䅅免䅁䩁䕷䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊佂䙁䅧䅊硁䑁䅧䅁捁元䅁䅥䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑杔奂䍁䅑兏䅁䩁䔰䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊佂䙁䅫䅊硁䑁䅅䅁婂杂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑杔婂䍁䅑免㑁䅁䅁先䅫䡁䅧䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䕁䄴兗歁䑁䅫䅁慂杂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑杔慂䍁䅑免硁䅁䅁眵䅍䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䕁䄴杗歁䑁䅅䅏䅁䉁䨴䅁㑂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊佂䙁䅯䅊㕁䅁䅁䄶䅍䡁䅧䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䕁䄸䅊硁䑁䅅䅁剁䅂䅁䅥䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑睔歁䑁䅅䅏䅁䍁䤴䅁㉂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊偂䍁䅑兏䅁䉁䕉䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊偂䕁䅅䅊硁䑁䅅䅁獃睂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑睔䉂䍁䅑免㑁䅁䅁䅉䅫䡁䅧䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䕁䄸兑歁䑁䅫䅁瑃睂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑睔䍂䍁䅑免硁䅁䅁睲䅣䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䕁䄸村歁䑁䅅䅏䅁䅁䡷䅁㑂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊偂䕁䅉䅊㕁䅁䅁兄䅣䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䕁䄸睑歁䑁䅅免䅁䱁䡁䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊偂䕁䅍䅊硁䑁䅧䅁楂䅃䅁䅥䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑睔䑂䍁䅑兏䅁䱁䡅䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊偂䕁䅑䅊硁䑁䅅䅁杁杂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑睔䕂䍁䅑免㑁䅁䅁兆䅫䡁䅧䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䕁䄸䅒歁䑁䅫䅁桁杂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑睔䙂䍁䅑免硁䅁䅁睌䅙䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䕁䄸兒歁䑁䅅䅏䅁䉁䠰䅁㑂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊偂䕁䅕䅊㕁䅁䅁䅍䅙䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䕁䄸杒歁䑁䅅免䅁䱁䡍䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊偂䕁䅙䅊硁䑁䅧䅁㑁兂䅁䅥䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑睔䝂䍁䅑兏䅁䑁䙫䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊偂䕁䅣䅊硁䑁䅅䅁ぃ睂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑睔䡂䍁䅑免㑁䅁䅁䅁䅧䡁䅧䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䕁䄸睒歁䑁䅫䅁ㅃ睂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑睔䥂䍁䅑免硁䅁䅁儴䅙䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䕁䄸䅓歁䑁䅅䅏䅁䉁䝕䅁㑂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊偂䕁䅧䅊㕁䅁䅁杆䅙䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䕁䄸兓歁䑁䅅免䅁䱁䡫䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊偂䕁䅫䅊硁䑁䅧䅁晃䅃䅁䅥䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑睔䩂䍁䅑兏䅁䱁䡯䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊偂䕁䅯䅊硁䑁䅅䅁㡃睂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑睔䭂䍁䅑免㑁䅁䅁光䅫䡁䅧䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䕁䄸杓歁䑁䅫䅁㥃睂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑睔䱂䍁䅑免硁䅁䅁兕䅕䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䕁䄸睓歁䑁䅅䅏䅁䱁䡙䅁㑂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊偂䕁䅳䅊㕁䅁䅁杕䅕䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䕁䄸䅔歁䑁䅅免䅁䱁䠸䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊偂䕁䅷䅊硁䑁䅧䅁噄䅃䅁䅥䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑睔䵂䍁䅑兏䅁䵁䡁䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊偂䕁䄰䅊硁䑁䅅䅁䑄睂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑睔乂䍁䅑免㑁䅁䅁杉䅫䡁䅧䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䕁䄸兔歁䑁䅫䅁䕄睂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑睔佂䍁䅑免硁䅁䅁典䅣䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䕁䄸杔歁䑁䅅䅏䅁佁䡳䅁㑂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊偂䕁䄴䅊㕁䅁䅁杸䅣䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䕁䄸睔歁䑁䅅免䅁䵁䡣䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊偂䕁䄸䅊硁䑁䅧䅁橁元䅁䅥䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑睔偂䍁䅑兏䅁䵁䡧䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊偂䙁䅁䅊硁䑁䅅䅁䩄睂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑睔兂䍁䅑免㑁䅁䅁眳䅕䡁䅧䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䕁䄸䅕歁䑁䅫䅁杄兂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑睔剂䍁䅑免硁䅁䅁䄸䅕䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䕁䄸兕歁䑁䅅䅏䅁䕁䙯䅁㑂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊偂䙁䅅䅊㕁䅁䅁睓䅕䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䕁䄸杕歁䑁䅅免䅁䅁䡧䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊偂䙁䅉䅊硁䑁䅧䅁歁元䅁䅥䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑睔卂䍁䅑兏䅁䅁䡫䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊偂䙁䅍䅊硁䑁䅅䅁塄兂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑睔呂䍁䅑免㑁䅁䅁杧䅍䡁䅧䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䕁䄸睕歁䑁䅫䅁䑃睁䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑睔啂䍁䅑免硁䅁䅁睭䅙䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䕁䄸䅖歁䑁䅅䅏䅁䍁䩕䅁㑂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊偂䙁䅑䅊㕁䅁䅁䅮䅙䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䕁䄸兖歁䑁䅅免䅁䅁䙣䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊偂䙁䅕䅊硁䑁䅧䅁流元䅁䅥䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑睔噂䍁䅑兏䅁䅁䙧䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊偂䙁䅙䅊硁䑁䅅䅁潃䅂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑睔坂䍁䅑免㑁䅁䅁眯䅍䡁䅧䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䕁䄸杖歁䑁䅫䅁䅁䅂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑睔塂䍁䅑免硁䅁䅁杶䅙䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䕁䄸睖歁䑁䅅䅏䅁䥁䝷䅁㑂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊偂䙁䅣䅊㕁䅁䅁兪䅙䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䕁䄸䅗歁䑁䅅免䅁䙁䘰䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊偂䙁䅧䅊硁䑁䅧䅁婂兂䅁䅥䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑睔奂䍁䅑兏䅁䙁䙯䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊偂䙁䅫䅊硁䑁䅅䅁䭄睂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑睔婂䍁䅑免㑁䅁䅁睊䅫䡁䅧䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䕁䄸兗歁䑁䅫䅁䱄睂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑睔慂䍁䅑免硁䅁䅁兺䅣䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䕁䄸杗歁䑁䅅䅏䅁䍁䩧䅁㑂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊偂䙁䅯䅊㕁䅁䅁杺䅣䡁䅧䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅁䅊硁䑁䅅䅁噁䅂䅁䅥䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑䅕歁䑁䅅䅏䅁䍁䤸䅁㉂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊兂䍁䅑兏䅁䉁䕙䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊兂䕁䅅䅊硁䑁䅅䅁兄睂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑䅕䉂䍁䅑免㑁䅁䅁克䅫䡁䅧䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅁兑歁䑁䅫䅁剄睂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑䅕䍂䍁䅑免硁䅁䅁睴䅣䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅁村歁䑁䅅䅏䅁䍁䡕䅁㑂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊兂䕁䅉䅊㕁䅁䅁杊䅣䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅁睑歁䑁䅅免䅁䑁䝙䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊兂䕁䅍䅊硁䑁䅧䅁㡃兂䅁䅥䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑䅕䑂䍁䅑兏䅁䱁䘰䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊兂䕁䅑䅊硁䑁䅅䅁硄兂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑䅕䕂䍁䅑免㑁䅁䅁䅥䅣䡁䅧䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅁䅒歁䑁䅫䅁祄兂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑䅕䙂䍁䅑免硁䅁䅁杘䅑䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅁兒歁䑁䅅䅏䅁䍁䩯䅁㑂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊兂䕁䅕䅊㕁䅁䅁睘䅑䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅁杒歁䑁䅅免䅁乁䡉䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊兂䕁䅙䅊硁䑁䅧䅁佃䅃䅁䅥䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑䅕䝂䍁䅑兏䅁乁䡍䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊兂䕁䅣䅊硁䑁䅅䅁啄睂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑䅕䡂䍁䅑免㑁䅁䅁睗䅙䡁䅧䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅁睒歁䑁䅫䅁捂杂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑䅕䥂䍁䅑免硁䅁䅁朱䅣䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅁䅓歁䑁䅅䅏䅁䵁䥯䅁㑂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊兂䕁䅧䅊㕁䅁䅁眱䅣䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅁兓歁䑁䅅免䅁乁䡧䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊兂䕁䅫䅊硁䑁䅧䅁牁元䅁䅥䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑䅕䩂䍁䅑兏䅁乁䡫䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊兂䕁䅯䅊硁䑁䅅䅁扄睂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑䅕䭂䍁䅑免㑁䅁䅁睄䅫䡁䅧䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅁杓歁䑁䅫䅁捄睂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑䅕䱂䍁䅑免硁䅁䅁儳䅣䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅁睓歁䑁䅅䅏䅁䅁䕳䅁㑂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊兂䕁䅳䅊㕁䅁䅁䅄䅑䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅁䅔歁䑁䅅免䅁乁䠸䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊兂䕁䅷䅊硁䑁䅧䅁䑁杂䅁䅥䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑䅕䵂䍁䅑兏䅁䅁䝑䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊兂䕁䄰䅊硁䑁䅅䅁桄睂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑䅕乂䍁䅑免㑁䅁䅁児䅧䡁䅧䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅁兔歁䑁䅫䅁楄睂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑䅕佂䍁䅑免硁䅁䅁睷䅙䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅁杔歁䑁䅅䅏䅁䍁䩷䅁㑂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊兂䕁䄴䅊㕁䅁䅁䅸䅙䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅁睔歁䑁䅅免䅁乁䑁䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊兂䕁䄸䅊硁䑁䅧䅁杄睂䅁䅥䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑䅕偂䍁䅑兏䅁乁䑅䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊兂䙁䅁䅊硁䑁䅅䅁浄杂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑䅕兂䍁䅑免㑁䅁䅁兴䅑䡁䅧䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅁䅕歁䑁䅫䅁㉃䅂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑䅕剂䍁䅑免硁䅁䅁䄵䅣䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅁兕歁䑁䅅䅏䅁䍁䨰䅁㑂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊兂䙁䅅䅊㕁䅁䅁儵䅣䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅁杕歁䑁䅅免䅁偁䘸䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊兂䙁䅉䅊硁䑁䅧䅁畁元䅁䅥䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑䅕卂䍁䅑兏䅁䅁䝁䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊兂䙁䅍䅊硁䑁䅅䅁楂兂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑䅕呂䍁䅑免㑁䅁䅁䄶䅧䡁䅧䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅁睕歁䑁䅫䅁橂兂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑䅕啂䍁䅑免硁䅁䅁眵䅣䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅁䅖歁䑁䅅䅏䅁䍁䥣䅁㑂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊兂䙁䅑䅊㕁䅁䅁䄶䅣䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅁兖歁䑁䅅免䅁佁䡯䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊兂䙁䅕䅊硁䑁䅧䅁乁杂䅁䅥䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑䅕噂䍁䅑兏䅁䅁䜴䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊兂䙁䅙䅊硁䑁䅅䅁獄睂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑䅕坂䍁䅑免㑁䅁䅁睌䅫䡁䅧䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅁杖歁䑁䅫䅁瑄睂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑䅕塂䍁䅑免硁䅁䅁兦䅑䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅁睖歁䑁䅅䅏䅁䉁䝣䅁㑂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊兂䙁䅣䅊㕁䅁䅁杦䅑䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅁䅗歁䑁䅅免䅁佁䠸䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊兂䙁䅧䅊硁䑁䅧䅁睁元䅁䅥䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑䅕奂䍁䅑兏䅁偁䡁䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊兂䙁䅫䅊硁䑁䅅䅁畁䅂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑䅕婂䍁䅑免㑁䅁䅁朰䅕䡁䅧䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅁兗歁䑁䅫䅁癁䅂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑䅕慂䍁䅑免硁䅁䅁来䅕䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅁杗歁䑁䅅䅏䅁䑁䩅䅁㑂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊兂䙁䅯䅊㕁䅁䅁睥䅕䡁䅧䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅅䅊硁䑁䅅䅁煄睁䅁䅥䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑兕歁䑁䅅䅏䅁䑁䥁䅁㉂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊剂䍁䅑兏䅁佁䑳䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊剂䕁䅅䅊硁䑁䅅䅁硄睂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑兕䉂䍁䅑免㑁䅁䅁䅨䅣䡁䅧䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅅兑歁䑁䅫䅁䙃睂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑兕䍂䍁䅑免硁䅁䅁杊䅙䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅅村歁䑁䅅䅏䅁䑁䩉䅁㑂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊剂䕁䅉䅊㕁䅁䅁睊䅙䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅅睑歁䑁䅅免䅁䉁䝧䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊剂䕁䅍䅊硁䑁䅧䅁穁元䅁䅥䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑兕䑂䍁䅑兏䅁䉁䝫䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊剂䕁䅑䅊硁䑁䅅䅁䝄睁䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑兕䕂䍁䅑免㑁䅁䅁䅎䅫䡁䅧䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅅䅒歁䑁䅫䅁䡄睁䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑兕䙂䍁䅑免硁䅁䅁兢䅙䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅅兒歁䑁䅅䅏䅁䑁䩕䅁㑂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊剂䕁䅕䅊㕁䅁䅁杢䅙䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅅杒歁䑁䅅免䅁偁䡍䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊剂䕁䅙䅊硁䑁䅧䅁㉁元䅁䅥䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑兕䝂䍁䅑兏䅁偁䡑䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊剂䕁䅣䅊硁䑁䅅䅁㉄睂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑兕䡂䍁䅑免㑁䅁䅁睎䅫䡁䅧䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅅睒歁䑁䅫䅁㍄睂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑兕䥂䍁䅑免硁䅁䅁杲䅕䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅅䅓歁䑁䅅䅏䅁䥁䥣䅁㑂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊剂䕁䅧䅊㕁䅁䅁睲䅕䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅅兓歁䑁䅅免䅁偁䡧䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊剂䕁䅫䅊硁䑁䅧䅁灁䅃䅁䅥䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑兕䩂䍁䅑兏䅁偁䡫䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊剂䕁䅯䅊硁䑁䅅䅁㙄睂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑兕䭂䍁䅑免㑁䅁䅁䅏䅫䡁䅧䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅅杓歁䑁䅫䅁㝄睂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑兕䱂䍁䅑免硁䅁䅁䅵䅣䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅅睓歁䑁䅅䅏䅁䕁䙕䅁㑂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊剂䕁䅳䅊㕁䅁䅁杒䅕䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅅䅔歁䑁䅅免䅁乁䝣䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊剂䕁䅷䅊硁䑁䅧䅁㕁元䅁䅥䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑兕䵂䍁䅑兏䅁乁䝧䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊剂䕁䄰䅊硁䑁䅅䅁奃䅂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑兕乂䍁䅑免㑁䅁䅁䅵䅧䡁䅧䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅅兔歁䑁䅫䅁婃䅂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑兕佂䍁䅑免硁䅁䅁䄯䅣䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅅杔歁䑁䅅䅏䅁䩁䙍䅁㑂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊剂䕁䄴䅊㕁䅁䅁䅬䅕䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅅睔歁䑁䅅免䅁偁䠴䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊剂䕁䄸䅊硁䑁䅧䅁佁兂䅁䅥䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑兕偂䍁䅑兏䅁䅁䘸䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊剂䙁䅁䅊硁䑁䅅䅁乁䅂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑兕兂䍁䅑免㑁䅁䅁眯䅑䡁䅧䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅅䅕歁䑁䅫䅁佁䅂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑兕剂䍁䅑免硁䅁䅁睱䅙䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅅兕歁䑁䅅䅏䅁䩁䡉䅁㑂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊剂䙁䅅䅊㕁䅁䅁䅲䅙䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣</t>
   </si>
   <si>
-    <t>光歁䙁䅅杕歁䑁䅅免䅁䵁䕫䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊剂䙁䅉䅊硁䑁䅧䅁㙁元䅁䅥䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑兕卂䍁䅑兏䅁䵁䕯䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊剂䙁䅍䅊硁䑁䅅䅁䥃䅂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑兕呂䍁䅑免㑁䅁䅁杲䅧䡁䅧䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅅睕歁䑁䅫䅁䩃䅂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑兕啂䍁䅑免硁䅁䅁䅡䅑䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅅䅖歁䑁䅅䅏䅁䅁䙫䅁㑂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊剂䙁䅑䅊㕁䅁䅁兡䅑䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅅兖歁䑁䅅免䅁䙁䠰䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊剂䙁䅕䅊硁䑁䅧䅁十元䅁䅥䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑兕噂䍁䅑兏䅁䙁䠴䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊剂䙁䅙䅊硁䑁䅅䅁䥃兂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑兕坂䍁䅑免㑁䅁䅁材䅧䡁䅧䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅅杖歁䑁䅫䅁䩃兂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑兕塂䍁䅑免硁䅁䅁杏䅙䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅅睖歁䑁䅅䅏䅁䭁䑯䅁㑂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊剂䙁䅣䅊㕁䅁䅁睱䅍䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅅䅗歁䑁䅅免䅁䅁䥅䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊剂䙁䅧䅊硁䑁䅧䅁奁䅂䅁䅥䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑兕奂䍁䅑兏䅁䉁䕫䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊剂䙁䅫䅊硁䑁䅅䅁扄兂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑兕婂䍁䅑免㑁䅁䅁睏䅫䡁䅧䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅅兗歁䑁䅫䅁捄兂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑兕慂䍁䅑免硁䅁䅁睁䅧䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅅杗歁䑁䅅䅏䅁乁䥷䅁㑂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊剂䙁䅯䅊㕁䅁䅁䅂䅧䡁䅧䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅉䅊硁䑁䅅䅁䥄睁䅁䅥䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑杕歁䑁䅅䅏䅁䍁䡣䅁㉂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊卂䍁䅑兏䅁䵁䑫䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊卂䕁䅅䅊硁䑁䅅䅁杁䅂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑杕䉂䍁䅑免㑁䅁䅁睎䅙䡁䅧䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅉兑歁䑁䅫䅁桁䅂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑杕䍂䍁䅑免硁䅁䅁杢䅑䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅉村歁䑁䅅䅏䅁䑁䩷䅁㑂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊卂䕁䅉䅊㕁䅁䅁睢䅑䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅉睑歁䑁䅅免䅁䅁䥕䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊卂䕁䅍䅊硁䑁䅧䅁㥁元䅁䅥䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑杕䑂䍁䅑兏䅁䅁䥙䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊卂䕁䅑䅊硁䑁䅅䅁䡁䅃䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑杕䕂䍁䅑免㑁䅁䅁兖䅣䡁䅧䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅉䅒歁䑁䅫䅁坂睂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑杕䙂䍁䅑免硁䅁䅁允䅑䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅉兒歁䑁䅅䅏䅁䝁䙧䅁㑂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊卂䕁䅕䅊㕁䅁䅁杁䅑䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅉杒歁䑁䅅免䅁䝁䝕䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊卂䕁䅙䅊硁䑁䅧䅁歁䅃䅁䅥䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑杕䝂䍁䅑兏䅁䝁䝙䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊卂䕁䅣䅊硁䑁䅅䅁䩁䅃䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑杕䡂䍁䅑免㑁䅁䅁材䅫䡁䅧䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅉睒歁䑁䅫䅁䭁䅃䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑杕䥂䍁䅑免硁䅁䅁睊䅕䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅉䅓歁䑁䅅䅏䅁䅁䙁䅁㑂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊卂䕁䅧䅊㕁䅁䅁允䅕䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅉兓歁䑁䅅免䅁䱁䠴䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊卂䕁䅫䅊硁䑁䅧䅁歄䅂䅁䅥䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑杕䩂䍁䅑兏䅁佁䕕䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊卂䕁䅯䅊硁䑁䅅䅁乁䅃䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑杕䭂䍁䅑免㑁䅁䅁睈䅫䡁䅧䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅉杓歁䑁䅫䅁佁䅃䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑杕䱂䍁䅑免硁䅁䅁睄䅧䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅉睓歁䑁䅅䅏䅁䑁䨸䅁㑂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊卂䕁䅳䅊㕁䅁䅁䅅䅧䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅉䅔歁䑁䅅免䅁䩁䕙䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊卂䕁䅷䅊硁䑁䅧䅁㑁䅃䅁䅥䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑杕䵂䍁䅑兏䅁䩁䕣䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊卂䕁䄰䅊硁䑁䅅䅁十䅃䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑杕乂䍁䅑免㑁䅁䅁睑䅙䡁䅧䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅉兔歁䑁䅫䅁䕂杂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑杕佂䍁䅑免硁䅁䅁睄䅣䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅉杔歁䑁䅅䅏䅁䡁䕣䅁㑂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊卂䕁䄴䅊㕁䅁䅁䅥䅑䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅉睔歁䑁䅅免䅁䉁䝯䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊卂䕁䄸䅊硁䑁䅧䅁獂䅃䅁䅥䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑杕偂䍁䅑兏䅁䉁䝳䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊卂䙁䅁䅊硁䑁䅅䅁呁䅃䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑杕兂䍁䅑免㑁䅁䅁䅦䅕䡁䅧䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅉䅕歁䑁䅫䅁㥂兂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑杕剂䍁䅑免硁䅁䅁眯䅣䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅉兕歁䑁䅅䅏䅁䉁䕯䅁㑂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊卂䙁䅅䅊㕁䅁䅁睇䅑䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅉杕歁䑁䅅免䅁䑁䙁䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊卂䙁䅉䅊硁䑁䅧䅁剂䅃䅁䅥䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑杕卂䍁䅑兏䅁䑁䙅䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊卂䙁䅍䅊硁䑁䅅䅁啁䅃䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑杕呂䍁䅑免㑁䅁䅁䅑䅫䡁䅧䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅉睕歁䑁䅫䅁噁䅃䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑杕啂䍁䅑免硁䅁䅁杆䅧䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅉䅖歁䑁䅅䅏䅁䕁䩅䅁㑂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊卂䙁䅑䅊㕁䅁䅁睆䅧䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅉兖歁䑁䅅免䅁䡁䠸䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊卂䙁䅕䅊硁䑁䅧䅁穂睁䅁䅥䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑杕噂䍁䅑兏䅁䡁䑑䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊卂䙁䅙䅊硁䑁䅅䅁噃兂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑杕坂䍁䅑免㑁䅁䅁村䅫䡁䅧䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅉杖歁䑁䅫䅁坃兂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑杕塂䍁䅑免硁䅁䅁䅇䅧䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅉睖歁䑁䅅䅏䅁䭁䝑䅁㑂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊卂䙁䅣䅊㕁䅁䅁兰䅙䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅉䅗歁䑁䅅免䅁䉁䥯䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊卂䙁䅧䅊硁䑁䅧䅁㥃䅃䅁䅥䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑杕奂䍁䅑兏䅁䉁䥳䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊卂䙁䅫䅊硁䑁䅅䅁捁䅃䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑杕婂䍁䅑免㑁䅁䅁睑䅫䡁䅧䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅉兗歁䑁䅫䅁摁䅃䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑杕慂䍁䅑免硁䅁䅁睕䅙䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅉杗歁䑁䅅䅏䅁䵁䡅䅁㑂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊卂䙁䅯䅊㕁䅁䅁䅖䅙䡁䅧䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅍䅊硁䑁䅅䅁塁䅂䅁䅥䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑睕歁䑁䅅䅏䅁偁䑙䅁㉂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊呂䍁䅑兏䅁偁䑣䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊呂䕁䅅䅊硁䑁䅅䅁橄睂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑睕䉂䍁䅑免㑁䅁䅁䅨䅍䡁䅧䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅍兑歁䑁䅫䅁䙃睁䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑睕䍂䍁䅑免硁䅁䅁睈䅣䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅍村歁䑁䅅䅏䅁䕁䩑䅁㑂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊呂䕁䅉䅊㕁䅁䅁䅉䅣䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅍睑歁䑁䅅免䅁䉁䝅䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊呂䕁䅍䅊硁䑁䅧䅁䱁元䅁䅥䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑睕䑂䍁䅑兏䅁䉁䝉䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊呂䕁䅑䅊硁䑁䅅䅁獄睁䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑睕䕂䍁䅑免㑁䅁䅁兒䅫䡁䅧䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅍䅒歁䑁䅫䅁瑄睁䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑睕䙂䍁䅑免硁䅁䅁兮䅣䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅍兒歁䑁䅅䅏䅁䕁䩙䅁㑂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊呂䕁䅕䅊㕁䅁䅁杮䅣䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅍杒歁䑁䅅免䅁䉁䤴䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊呂䕁䅙䅊硁䑁䅧䅁䡂元䅁䅥䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑睕䝂䍁䅑兏䅁䉁䤸䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊呂䕁䅣䅊硁䑁䅅䅁杁䅃䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑睕䡂䍁䅑免㑁䅁䅁䅎䅣䡁䅧䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅍睒歁䑁䅫䅁ㅁ睂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑睕䥂䍁䅑免硁䅁䅁眴䅕䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅍䅓歁䑁䅅䅏䅁佁䙧䅁㑂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊呂䕁䅧䅊㕁䅁䅁䄵䅕䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅍兓歁䑁䅅免䅁䩁䜸䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊呂䕁䅫䅊硁䑁䅧䅁䥂元䅁䅥䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑睕䩂䍁䅑兏䅁䭁䝁䅁㑂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊啂䍁䅑免硁䅁䅁䅈䅑䡁䅧䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅑䅊硁䑁䅧䅁䵂睂䅁杤䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑䅖歁䑁䅫䅁摁䅂䅁䅥䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑兖歁䑁䅅免䅁䅁䕍䅁㑂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊噂䍁䅑免㑁䅁䅁睍䅧䡁䅙䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅕䅊㕁䅁䅁䅂䅑䡁䅧䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅙䅊硁䑁䅅䅁祃睁䅁䅥䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑杖歁䑁䅅䅏䅁䡁䝯䅁㉂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊坂䍁䅑兏䅁䱁䑍䅁㑂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊塂䍁䅑免硁䅁䅁杬䅍䡁䅧䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅣䅊硁䑁䅧䅁ぁ䅃䅁杤䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑睖歁䑁䅫䅁塃睁䅁䅥䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑䅗歁䑁䅅免䅁䭁䐴䅁㑂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊奂䍁䅑免㑁䅁䅁杸䅙䡁䅙䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅧䅊㕁䅁䅁睲䅍䡁䅧䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅫䅊硁䑁䅅䅁慃睁䅁䅥䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑兗歁䑁䅅䅏䅁䝁䘰䅁㉂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊婂䍁䅑兏䅁䩁䑳䅁㑂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊慂䍁䅑免硁䅁䅁兊䅑䡁䅧䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅯䅊硁䑁䅧䅁呃䅂䅁杤䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑杗歁䑁䅫䅁流䅂䅁䅔䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅧党求䡁䅑睍桁䍁䅑睒歁䑁䅉䅁奂睁䅁䅔䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅧党求䡁䅑睍桁䍁䅑䅓歁䑁䅉䅁扂睁䅁杙䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘療䡁䅉䅚求䡁䅉杌楂䝁䅅睙牂䝁䅷睢湂䍁䄴睙潂䝁䅣光歁䕁䅅䅊ㅁ䅁䅁杓䅫䝁䅉䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睢祂䝁䅑党祂䍁䄴杙桂䝁䅍睡獂䝁䄸睚畁䝁䅍䅡湂䍁䅅䅊䉂䍁䅑睎䅁䕁䩫䅁楂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑杒歁䑁䅅䅁䅁䅁䅁权䅁䝁䄴睢㉂䝁䅅䅁㙁睁䅁杈䅁䡁䅍䅡療䡁䅉䅤杁䝁䅫杢あ䝁䅕杣求䡁䅍䅤䅁䙁䑁䅁潁䅁䅁䍄䉁䅁䅁杂䅁䅁䅍睄䅁䅁䅕䅁䅁䑁䝒䕅䭅䙁䩍䅁䭁䅁䍙䅁䭁䅁䍙䅁䭁䕁䩷䅁䉁䅁䅁允䅁䅁䅯兯䅫䅁杷允䅁䅁䅙䅁䑁䅁䄸䅁䙁䅁䅁䅁ぁ桒䉂权䱃元䅁权䝁杁䅁权䝁杁䅁权䵂元䅁允䅁䅁䅅䅁䭁䭁䩁䅁䵁䅉䅅䅁䙁䅁䅁睁偁䅁䅁兂䅁䅁䅁䕎兙兑䅯入䅫䅁䅯䅂䍁䅧䅯睤䅫䅁䅅䅁䉁䅁䅁权ㅂ元䅁䍄䉁䅁䅁杂䅁䅁䅍睄䅁䅁䅕䅁䅁䑁䝒䕅䭅䙁䩅䅁䭁䅁䍙䅁䭁䅁䍙䅁䭁䕁䩷䅁䉁䅁䅁允䅁䅁䅯兮䅫䅁杷允䅁䅁䅙䅁䑁䅁䄸䅁䙁䅁䅁䅁ぁ桒䉂权䡃元䅁权䝁杁䅁权䝁杁䅁权䵂元䅁允䅁䅁䅅䅁䭁䭁䩑䅁䵁䅉䅅䅁䝁䅁䅁睁偁䅁䅁兂䅁䅁䅁䕎兙兑䅯睓䅫䅁䅯杂䅉䅁䅯杂䅉䅁䅯䅔䅫䅁䅅䅁䉁䅁䅁权敃元䅁䍄䉁䅁䅁杂䅁䅁䅍睄䅁䅁䅕䅁䅁䑁䝒䕅䭅䙁䩧䅁䭁䅁䍙䅁䭁䅁䍙䅁䭁䕁䩷䅁䉁䅁䅁允䅁䅁䅯兗䅫䅁杷允䅁䅁䅕䅁䑁䅁䄸䅁䙁䅁䅁䅁ぁ桒䉂权摂元䅁权䕁䅁䅋权歂元䅁允䅁䅁䅅䅁䭁䙁䨸䅁䵁䅉䅅䅁䝁䅁䅁睁偁䅁䅁兂䅁䅁䅁䕎兙兑䅯睧䅫䅁䅯杂䅉䅁䅯杂䅉䅁䅯䅔䅫䅁䅅䅁䉁䅁䅁权晃元䅁䍄䉁䅁䅁杂䅁䅁䅍睄䅁䅁䅕䅁䅁䑁䝒䕅䭅䙁䩯䅁䭁䅁䍙䅁䭁䅁䍙䅁䭁䕁䩷䅁䉁䅁䅁允䅁䅁䅯睗䅫䅁杷允䅁䅁䅙䅁䑁䅁䄸䅁䙁䅁䅁䅁ぁ桒䉂权湂元䅁权䝁杁䅁权䝁杁䅁权䵂元䅁允䅁䅁䅅䅁䭁䝁䩧䅁䵁䅉䅅䅁䝁䅁䅁睁偁䅁䅁兂䅁䅁䅁䕎兙兑䅯兖䅫䅁䅯杂䅉䅁䅯䅘䅫䅁䅯䅔䅫䅁䅅䅁䉁䅁䅁权塂元䅁䍄䉁䅁䅁杂䅁䅁䅍睄䅁䅁䅕䅁䅁䑁䝒䕅䭅䙁䨰䅁䭁䙁䨴䅁䭁䙁䨸䅁䭁䕁䩷䅁䉁䅁䅁允䅁䅁䅯杯䅫䅁杷允䅁䅁䅙䅁䑁䅁䄸䅁䙁䅁䅁䅁ぁ桒䉂权㕂元䅁权䝁杁䅁权ㅂ元䅁权䵂元䅁允䅁䅁䅅䅁䭁䡁䩯䅁䵁䅉䅅䅁䝁䅁䅁睁偁䅁䅁兂䅁䅁䅁䕎兙兑䅯杢䅫䅁䅯杂䅉䅁䅯杂䅉䅁䅯䅔䅫䅁䅅䅁䉁䅁䅁权橃元䅁䍄䉁䅁䅁杂䅁䅁䅍睄䅁䅁䅕䅁䅁䑁䝒䕅䭅䝁䩅䅁䭁䙁䨴䅁䭁䙁䨸䅁䭁䕁䩷䅁䉁䅁䅁允䅁䅁䅯杙䅫䅁杷允䅁䅁䅙䅁䑁䅁䄸䅁䙁䅁䅁䅁ぁ桒䉂权噂元䅁权䝁杁䅁权ㅂ元䅁权䵂元䅁允䅁䅁䅅䅁䭁䙁䩣䅁䵁䅉䅅䅁䝁䅁䅁睁偁䅁䅁兂䅁䅁䅁䕎兙兑䅯睦䅫䅁䅯䅧䅫䅁䅯杂䅉䅁䅯䅔䅫䅁䅅䅁䉁䅁䅁权湃元䅁䍄䉁䅁䅁杂䅁䅁䅍睄䅁䅁䅕䅁䅁䑁䝒䕅䭅䙁䩕䅁䭁䅁䍙䅁䭁䡁䩙䅁䭁䕁䩷䅁䉁䅁䅁允䅁䅁䅯睖䅫䅁杷允䅁䅁䅑䅁䑁䅁䄸䅁䙁䅁䅁䅁ぁ桒䉂权摂元䅁权橂元䅁允䅁䅁䅅䅁䭁䙁䨴䅁䵁䅉䅅䅁䝁䅁䅁睁偁䅁䅁兂䅁䅁䅁䕎兙兑䅯兖䅫䅁䅯杂䅉䅁䅯杖䅫䅁䅯䅔䅫䅁䅅䅁䉁䅁䅁权塂元䅁䍄䉁䅁䅁䅂䅁䅁䅍睄䅁䅁䅕䅁䅁䑁䝒䕅䭅䝁䩅䅁䭁䝁䩍䅁䉁䅁䅁允䅁䅁䅯杘䅫䅁杷允䅁䅁䅕䅁䑁䅁䄸䅁䙁䅁䅁䅁ぁ桒䉂权桂元䅁权䕁䅁䅋权歂元䅁允䅁䅁䅅䅁䭁䙁䨸䅁䵁䅉䅅䅁䙁䅁䅁睁偁䅁䅁兂䅁䅁䅁䕎兙兑䅯兖䅫䅁䅯䅂䍁䅧䅯党䅫䅁䅅䅁䉁䅁䅁权捂元䅁䍄䉁䅁䅁兂䅁䅁䅍睄䅁䅁䅕䅁䅁䑁䝒䕅䭅䙁䩕䅁䭁䅁䅑潁䭁䡁䩣䅁䉁䅁䅁允䅁䅁䅯兤䅫䅁杷允䅁䅁䅙䅁䑁䅁䄸䅁䙁䅁䅁䅁ぁ桒䉂权䙃元䅁权䝁杁䅁权䝁杁䅁权䵂元䅁允䅁䅁䅅䅁䭁䥁䩙䅁䵁䅉䅅䅁䙁䅁䅁睁偁䅁䅁兂䅁䅁䅁䕎兙兑䅯兖䅫䅁䅯䅂䍁䅧䅯䅥䅫䅁䅅䅁䉁䅁䅁权㉂元䅁䍄䉁䅁䅁兂䅁䅁䅍睄䅁䅁䅕䅁䅁䑁䝒䕅䭅䡁䩫䅁䭁䅁䅑潁䭁䝁䩕䅁䉁䅁䅁允䅁䅁䅯䅘䅫䅁杷允䅁䅁䅑䅁䑁䅁䄸䅁䙁䅁䅁䅁ぁ桒䉂权⽂元䅁权䍃元䅁允䅁䅁䅅䅁䭁䥁䩁䅁䵁䅉䅅䅁䝁䅁䅁睁偁䅁䅁兂䅁䅁䅁䕎兙兑䅯䅢䅫䅁䅯杂䅉䅁䅯杂䅉䅁䅯䅔䅫䅁䅅䅁䉁䅁䅁权汃元䅁䍄䉁䅁䅁杂䅁䅁䅍睄䅁䅁䅕䅁䅁䑁䝒䕅䭅䡁䨰䅁䭁䅁䍙䅁䭁䅁䍙䅁䭁䕁䩷䅁䉁䅁䅁允䅁䅁䅯杰䅫䅁杷允䅁䅁䅙䅁䑁䅁䄸䅁䙁䅁䅁䅁ぁ桒䉂权㕂元䅁权䝁杁䅁权捂元䅁权䵂元䅁允䅁䅁䅅䅁䭁䡁䩯䅁䵁䅉䅅䅁䙁䅁䅁睁偁䅁䅁兂䅁䅁䅁䕎兙兑䅯兪䅫䅁䅯䅂䍁䅧䅯睤䅫䅁䅅䅁䉁䅁䅁权ㅂ元䅁䍄䉁䅁䅁杂䅁䅁䅍睄䅁䅁䅕䅁䅁䑁䝒䕅䭅䥁䩫䅁䭁䅁䍙䅁䭁䅁䍙䅁䭁䕁䩷䅁䉁䅁䅁允䅁䅁䅯䅱䅫䅁杷允䅁䅁䅙䅁䑁䅁䄸䅁䙁䅁䅁䅁ぁ桒䉂权䵂睁䅁权䝁杁䅁权䝁杁䅁权䵂元䅁允䅁䅁䅅䅁䭁䝁䩫䅁䵁䅉䅅䅁䝁䅁䅁睁偁䅁䅁兂䅁䅁䅁䕎兙兑䅯兪䅫䅁䅯杂䅉䅁䅯兤䅫䅁䅯䅔䅫䅁䅅䅁䉁䅁䅁权佃元䅁䍄䉁䅁䅁䅃䅁䅁杷允䅁䅁䅕䅁䭁䭁䨸䅁䭁䱁䩁䅁䭁䱁䩅䅁䭁䅁䅑潁䭁䕁䩷䅁啁䙁⽴䭅硏杦乕䅆㥁䙕摥㡃癧剤䅑䥩䱉㑘椱䅚啯䡁潍祳㠳䅋瘵䅆歂㕖䡨㡤煯割䅑瑬湮猷㙂㑶唰䝁塒䕭㍤楹瑱允䅁䅁䅅䅁䭁䩁䩉䅁䵁䅉䅅䅁䥁䅁䅁䍄䉁䅁䅁兂䅁䅁䅯共䅫䅁䅯東䅫䅁䅯睱䅫䅁䅯䅂䍁䅧䅯䅔䅫䉁䅑㍗儸㝯⭆兂唰䑁儱㕖䰰䍹ㄹ䅆䉃婉瑹䉋睖剄䅑䭳牸橊潰呣唴䝁塒䕭㍤楹瑱䅆坃攲畦䡷⽱剪䅑䙚奥㍒䭦煋䈰䅁䅁允䅁䅁䅯杫䅫䅁杷允䅁䅁䅧䅁䵁䅉䅅䅁䙁䅁䅁权獃元䅁权瑃元䅁权畃元䅁权䕁䅁䅋权䵂元䅁䅆扂硦橃塳䘴剄䅑噐塂兮䥶㍌啕佁灕㍇䥨㠶乭䅆癁䍉昶㍉㑘䉫䅑䙚奥㍒䭦煋唰䩁婢⬵䄷牥丫䅆歂㕖䡨㡤煯兲䅅䅁䉁䅁䅁权千元䅁䍄䉁䅁䅁兂䅁䅁䅍睄䅁䅁䅕䅁䅁䑁䝒䕅䭅䙁䩕䅁䭁䅁䅑潁䭁䝁䩙䅁䉁䅁䅁允䅁䅁䅯杖䅫䅁㴽</t>
+    <t>光歁䙁䅅杕歁䑁䅅免䅁䵁䕫䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊剂䙁䅉䅊硁䑁䅧䅁㙁元䅁䅥䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑兕卂䍁䅑兏䅁䵁䕯䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊剂䙁䅍䅊硁䑁䅅䅁䥃䅂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑兕呂䍁䅑免㑁䅁䅁杲䅧䡁䅧䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅅睕歁䑁䅫䅁䩃䅂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑兕啂䍁䅑免硁䅁䅁䅡䅑䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅅䅖歁䑁䅅䅏䅁䅁䙫䅁㑂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊剂䙁䅑䅊㕁䅁䅁兡䅑䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅅兖歁䑁䅅免䅁䙁䠰䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊剂䙁䅕䅊硁䑁䅧䅁十元䅁䅥䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑兕噂䍁䅑兏䅁䙁䠴䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊剂䙁䅙䅊硁䑁䅅䅁䥃兂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑兕坂䍁䅑免㑁䅁䅁材䅧䡁䅧䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅅杖歁䑁䅫䅁䩃兂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑兕塂䍁䅑免硁䅁䅁杏䅙䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅅睖歁䑁䅅䅏䅁䭁䑯䅁㑂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊剂䙁䅣䅊㕁䅁䅁睱䅍䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅅䅗歁䑁䅅免䅁䅁䥅䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊剂䙁䅧䅊硁䑁䅧䅁奁䅂䅁䅥䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑兕奂䍁䅑兏䅁䉁䕫䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊剂䙁䅫䅊硁䑁䅅䅁扄兂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑兕婂䍁䅑免㑁䅁䅁睏䅫䡁䅧䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅅兗歁䑁䅫䅁捄兂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑兕慂䍁䅑免硁䅁䅁睁䅧䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅅杗歁䑁䅅䅏䅁乁䥷䅁㑂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊剂䙁䅯䅊㕁䅁䅁䅂䅧䡁䅧䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅉䅊硁䑁䅅䅁䥄睁䅁䅥䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑杕歁䑁䅅䅏䅁䍁䡣䅁㉂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊卂䍁䅑兏䅁䵁䑫䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊卂䕁䅅䅊硁䑁䅅䅁杁䅂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑杕䉂䍁䅑免㑁䅁䅁睎䅙䡁䅧䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅉兑歁䑁䅫䅁桁䅂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑杕䍂䍁䅑免硁䅁䅁杢䅑䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅉村歁䑁䅅䅏䅁䑁䩷䅁㑂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊卂䕁䅉䅊㕁䅁䅁睢䅑䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅉睑歁䑁䅅免䅁䅁䥕䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊卂䕁䅍䅊硁䑁䅧䅁㥁元䅁䅥䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑杕䑂䍁䅑兏䅁䅁䥙䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊卂䕁䅑䅊硁䑁䅅䅁䡁䅃䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑杕䕂䍁䅑免㑁䅁䅁兖䅣䡁䅧䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅉䅒歁䑁䅫䅁坂睂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑杕䙂䍁䅑免硁䅁䅁允䅑䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅉兒歁䑁䅅䅏䅁䝁䙧䅁㑂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊卂䕁䅕䅊㕁䅁䅁杁䅑䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅉杒歁䑁䅅免䅁䝁䝕䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊卂䕁䅙䅊硁䑁䅧䅁歁䅃䅁䅥䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑杕䝂䍁䅑兏䅁䝁䝙䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊卂䕁䅣䅊硁䑁䅅䅁䩁䅃䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑杕䡂䍁䅑免㑁䅁䅁材䅫䡁䅧䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅉睒歁䑁䅫䅁䭁䅃䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑杕䥂䍁䅑免硁䅁䅁睊䅕䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅉䅓歁䑁䅅䅏䅁䅁䙁䅁㑂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊卂䕁䅧䅊㕁䅁䅁允䅕䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅉兓歁䑁䅅免䅁䱁䠴䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊卂䕁䅫䅊硁䑁䅧䅁歄䅂䅁䅥䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑杕䩂䍁䅑兏䅁佁䕕䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊卂䕁䅯䅊硁䑁䅅䅁乁䅃䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑杕䭂䍁䅑免㑁䅁䅁睈䅫䡁䅧䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅉杓歁䑁䅫䅁佁䅃䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑杕䱂䍁䅑免硁䅁䅁睄䅧䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅉睓歁䑁䅅䅏䅁䑁䨸䅁㑂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊卂䕁䅳䅊㕁䅁䅁䅅䅧䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅉䅔歁䑁䅅免䅁䩁䕙䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊卂䕁䅷䅊硁䑁䅧䅁㑁䅃䅁䅥䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑杕䵂䍁䅑兏䅁䩁䕣䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊卂䕁䄰䅊硁䑁䅅䅁十䅃䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑杕乂䍁䅑免㑁䅁䅁睑䅙䡁䅧䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅉兔歁䑁䅫䅁䕂杂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑杕佂䍁䅑免硁䅁䅁睄䅣䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅉杔歁䑁䅅䅏䅁䡁䕣䅁㑂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊卂䕁䄴䅊㕁䅁䅁䅥䅑䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅉睔歁䑁䅅免䅁䉁䝯䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊卂䕁䄸䅊硁䑁䅧䅁獂䅃䅁䅥䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑杕偂䍁䅑兏䅁䉁䝳䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊卂䙁䅁䅊硁䑁䅅䅁呁䅃䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑杕兂䍁䅑免㑁䅁䅁䅦䅕䡁䅧䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅉䅕歁䑁䅫䅁㥂兂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑杕剂䍁䅑免硁䅁䅁眯䅣䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅉兕歁䑁䅅䅏䅁䉁䕯䅁㑂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊卂䙁䅅䅊㕁䅁䅁睇䅑䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅉杕歁䑁䅅免䅁䑁䙁䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊卂䙁䅉䅊硁䑁䅧䅁剂䅃䅁䅥䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑杕卂䍁䅑兏䅁䑁䙅䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊卂䙁䅍䅊硁䑁䅅䅁啁䅃䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑杕呂䍁䅑免㑁䅁䅁䅑䅫䡁䅧䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅉睕歁䑁䅫䅁噁䅃䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑杕啂䍁䅑免硁䅁䅁杆䅧䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅉䅖歁䑁䅅䅏䅁䕁䩅䅁㑂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊卂䙁䅑䅊㕁䅁䅁睆䅧䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅉兖歁䑁䅅免䅁䡁䠸䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊卂䙁䅕䅊硁䑁䅧䅁穂睁䅁䅥䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑杕噂䍁䅑兏䅁䡁䑑䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊卂䙁䅙䅊硁䑁䅅䅁噃兂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑杕坂䍁䅑免㑁䅁䅁村䅫䡁䅧䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅉杖歁䑁䅫䅁坃兂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑杕塂䍁䅑免硁䅁䅁䅇䅧䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅉睖歁䑁䅅䅏䅁䭁䝑䅁㑂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊卂䙁䅣䅊㕁䅁䅁兰䅙䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅉䅗歁䑁䅅免䅁䉁䥯䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊卂䙁䅧䅊硁䑁䅧䅁㥃䅃䅁䅥䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑杕奂䍁䅑兏䅁䉁䥳䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊卂䙁䅫䅊硁䑁䅅䅁捁䅃䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑杕婂䍁䅑免㑁䅁䅁睑䅫䡁䅧䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅉兗歁䑁䅫䅁摁䅃䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑杕慂䍁䅑免硁䅁䅁睕䅙䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅉杗歁䑁䅅䅏䅁䵁䡅䅁㑂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊卂䙁䅯䅊㕁䅁䅁䅖䅙䡁䅧䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅍䅊硁䑁䅅䅁塁䅂䅁䅥䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑睕歁䑁䅅䅏䅁偁䑙䅁㉂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊呂䍁䅑兏䅁偁䑣䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊呂䕁䅅䅊硁䑁䅅䅁橄睂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑睕䉂䍁䅑免㑁䅁䅁䅨䅍䡁䅧䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅍兑歁䑁䅫䅁䙃睁䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑睕䍂䍁䅑免硁䅁䅁睈䅣䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅍村歁䑁䅅䅏䅁䕁䩑䅁㑂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊呂䕁䅉䅊㕁䅁䅁䅉䅣䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅍睑歁䑁䅅免䅁䉁䝅䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊呂䕁䅍䅊硁䑁䅧䅁䱁元䅁䅥䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑睕䑂䍁䅑兏䅁䉁䝉䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊呂䕁䅑䅊硁䑁䅅䅁獄睁䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑睕䕂䍁䅑免㑁䅁䅁兒䅫䡁䅧䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅍䅒歁䑁䅫䅁瑄睁䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑睕䙂䍁䅑免硁䅁䅁兮䅣䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅍兒歁䑁䅅䅏䅁䕁䩙䅁㑂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊呂䕁䅕䅊㕁䅁䅁杮䅣䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅍杒歁䑁䅅免䅁䉁䤴䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊呂䕁䅙䅊硁䑁䅧䅁䡂元䅁䅥䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑睕䝂䍁䅑兏䅁䉁䤸䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊呂䕁䅣䅊硁䑁䅅䅁杁䅃䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑睕䡂䍁䅑免㑁䅁䅁䅎䅣䡁䅧䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅍睒歁䑁䅫䅁ㅁ睂䅁来䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑睕䥂䍁䅑免硁䅁䅁眴䅕䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅍䅓歁䑁䅅䅏䅁佁䙧䅁㑂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊呂䕁䅧䅊㕁䅁䅁䄵䅕䡁䅯䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅍兓歁䑁䅅免䅁䩁䜸䅁㙂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊呂䕁䅫䅊硁䑁䅧䅁䥂元䅁䅥䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑睕䩂䍁䅑兏䅁䭁䝁䅁㑂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊啂䍁䅑免硁䅁䅁䅈䅑䡁䅧䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅑䅊硁䑁䅧䅁䵂睂䅁杤䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑䅖歁䑁䅫䅁摁䅂䅁䅥䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑兖歁䑁䅅免䅁䅁䕍䅁㑂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊噂䍁䅑免㑁䅁䅁睍䅧䡁䅙䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅕䅊㕁䅁䅁䅂䅑䡁䅧䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅙䅊硁䑁䅅䅁祃睁䅁䅥䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑杖歁䑁䅅䅏䅁䡁䝯䅁㉂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊坂䍁䅑兏䅁䱁䑍䅁㑂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊塂䍁䅑免硁䅁䅁杬䅍䡁䅧䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅣䅊硁䑁䅧䅁ぁ䅃䅁杤䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑睖歁䑁䅫䅁塃睁䅁䅥䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑䅗歁䑁䅅免䅁䭁䐴䅁㑂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊奂䍁䅑免㑁䅁䅁杸䅙䡁䅙䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅧䅊㕁䅁䅁睲䅍䡁䅧䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅫䅊硁䑁䅅䅁慃睁䅁䅥䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑兗歁䑁䅅䅏䅁䝁䘰䅁㉂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊婂䍁䅑兏䅁䩁䑳䅁㑂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䙁䅍睙祂䝁䅕党畂䝁䅫杢湂䙁䄸睢祂䝁䅑党祂䙁䄸杙桂䝁䅍睡獂䝁䄸睚時䝁䅍䅡湂䍁䅅䅊慂䍁䅑免硁䅁䅁兊䅑䡁䅧䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睕橂䡁䅉党求䝁䄴兡畂䝁䅣睘療䡁䅉䅚求䡁䅉睘楂䝁䅅睙牂䝁䅷睢湂䙁䄸睙潂䝁䅣光歁䙁䅯䅊硁䑁䅧䅁呃䅂䅁杤䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅍杣求䝁䅕杢灂䝁䄴睚時䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑杗歁䑁䅫䅁流䅂䅁䅔䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅧党求䡁䅑睍桁䍁䅑睒歁䑁䅉䅁奂睁䅁䅔䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘呂䝁䅧党求䡁䅑睍桁䍁䅑䅓歁䑁䅉䅁扂睁䅁杙䅁䙁䅳杣求䡁䅁䅢灂䝁䅍兙あ䝁䅫杢湂䙁䄸兙畂䝁䄸兢桂䝁䅷入畁䡁䅧䅢穂䡁䅧兘療䡁䅉䅚求䡁䅉杌楂䝁䅅睙牂䝁䅷睢湂䍁䄴睙潂䝁䅣光歁䕁䅅䅊ㅁ䅁䅁杓䅫䝁䅉䅁扂䡁䅉党睂䝁䅷兡橂䝁䅅䅤灂䝁䄴睚時䝁䅅杢療䝁䄰兙獂䡁䅫杌㑂䝁䅷督㑂䙁䄰睢祂䝁䅑党祂䍁䄴杙桂䝁䅍睡獂䝁䄸睚畁䝁䅍䅡湂䍁䅅䅊䉂䍁䅑睎䅁䕁䩫䅁楂䅁䅁睗祂䝁䅕䅣獂䝁䅫睙桂䡁䅑兡畂䝁䅣睘桂䝁䄴睢瑂䝁䅅䅢㕂䍁䄴䅥獂䡁䅍䅥摂䝁䄸杣歂䝁䅕杣時䝁䅉兙橂䝁䅳䅢療䝁䅣睘橂䝁䅧睚桁䍁䅑杒歁䑁䅅䅁䅁䅁䅁权䅁䝁䄴睢㉂䝁䅅䅁㙁睁䅁杈䅁䡁䅍䅡療䡁䅉䅤杁䝁䅫杢あ䝁䅕杣求䡁䅍䅤䅁䙁䑁䅁䉁䅁䅁䍄䉁䅁䅁䅃䅁䅁杷允䅁䅁䅕䅁䭁䭁䩷䅁䭁䭁䨰䅁䭁䭁䨴䅁䭁䅁䅑潁䭁䕁䩷䅁啁䙁⽴䭅硏杦乕䅆㥁䙕摥㡃癧剤䅑匵扫䕥牪她唰䍁朸灌樸晤兩䅆歂㕖䡨㡤煯割䅑瑬湮猷㙂㑶唰䝁塒䕭㍤楹瑱允䅁䅁䅅䅁䭁䩁䩉䅁㵁</t>
   </si>
 </sst>
 </file>
@@ -3650,7 +3650,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="3" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -3735,26 +3735,14 @@
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="3" fontId="0" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4071,29 +4059,29 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F77A7034-3063-43A0-9123-65366915E7EC}">
   <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>449</v>
       </c>
@@ -4106,18 +4094,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C28F445C-6D3D-4BF1-B640-BAD1596F14E8}">
   <dimension ref="A1:J213"/>
-  <sheetFormatPr defaultRowHeight="14.25" outlineLevelCol="1" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="45.46484375" style="32" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="2" max="3" width="47.6640625" style="32" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="4" max="4" width="46.33203125" style="32" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="5" max="5" width="6.46484375" style="29" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="6" max="6" width="45.46484375" style="21" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="7" max="8" width="12.33203125" style="21" customWidth="1"/>
-    <col min="9" max="10" width="12.33203125" customWidth="1"/>
+    <col min="1" max="1" width="45.42578125" style="32" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="2" max="3" width="47.7109375" style="32" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="4" max="4" width="46.28515625" style="32" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="5" max="5" width="6.42578125" style="29" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="6" max="6" width="45.42578125" style="21" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="7" max="8" width="12.28515625" style="21" customWidth="1"/>
+    <col min="9" max="10" width="12.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:10" s="19" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="30" t="s">
         <v>364</v>
       </c>
@@ -4131,20 +4119,20 @@
         <v>369</v>
       </c>
       <c r="E1" s="28"/>
-      <c r="G1" s="34" t="s">
+      <c r="G1" s="36" t="s">
         <v>371</v>
       </c>
-      <c r="H1" s="34" t="s">
+      <c r="H1" s="36" t="s">
         <v>372</v>
       </c>
-      <c r="I1" s="34" t="s">
+      <c r="I1" s="36" t="s">
         <v>373</v>
       </c>
-      <c r="J1" s="34" t="s">
+      <c r="J1" s="36" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="31" t="str">
         <f>Mom6m.Junk!A9</f>
         <v>MicroStrategy Incorporated (NASDAQGS:MSTR)</v>
@@ -4161,12 +4149,12 @@
         <f>Mom1m.Vol1m!A9</f>
         <v>MARA Holdings, Inc. (NASDAQCM:MARA)</v>
       </c>
-      <c r="G2" s="34"/>
-      <c r="H2" s="34"/>
-      <c r="I2" s="34"/>
-      <c r="J2" s="34"/>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="G2" s="36"/>
+      <c r="H2" s="36"/>
+      <c r="I2" s="36"/>
+      <c r="J2" s="36"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="31" t="str">
         <f>Mom6m.Junk!A10</f>
         <v>Carvana Co. (NYSE:CVNA)</v>
@@ -4184,12 +4172,12 @@
         <v>CleanSpark, Inc. (NASDAQCM:CLSK)</v>
       </c>
       <c r="F3"/>
-      <c r="G3" s="34"/>
-      <c r="H3" s="34"/>
-      <c r="I3" s="34"/>
-      <c r="J3" s="34"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="G3" s="36"/>
+      <c r="H3" s="36"/>
+      <c r="I3" s="36"/>
+      <c r="J3" s="36"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="31" t="str">
         <f>Mom6m.Junk!A11</f>
         <v>Vistra Corp. (NYSE:VST)</v>
@@ -4222,7 +4210,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="31" t="str">
         <f>Mom6m.Junk!A12</f>
         <v>Lumen Technologies, Inc. (NYSE:LUMN)</v>
@@ -4259,7 +4247,7 @@
         <v>Y</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="31" t="str">
         <f>Mom6m.Junk!A13</f>
         <v>Brinker International, Inc. (NYSE:EAT)</v>
@@ -4296,7 +4284,7 @@
         <v>Y</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="31" t="str">
         <f>Mom6m.Junk!A14</f>
         <v>IES Holdings, Inc. (NASDAQGM:IESC)</v>
@@ -4333,7 +4321,7 @@
         <v>Y</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="31" t="str">
         <f>Mom6m.Junk!A15</f>
         <v>Semtech Corporation (NASDAQGS:SMTC)</v>
@@ -4370,7 +4358,7 @@
         <v>N</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="31" t="str">
         <f>Mom6m.Junk!A16</f>
         <v>Carpenter Technology Corporation (NYSE:CRS)</v>
@@ -4407,7 +4395,7 @@
         <v>N</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="31" t="str">
         <f>Mom6m.Junk!A17</f>
         <v>Sprouts Farmers Market, Inc. (NASDAQGS:SFM)</v>
@@ -4444,7 +4432,7 @@
         <v>N</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="31" t="str">
         <f>Mom6m.Junk!A18</f>
         <v>The GEO Group, Inc. (NYSE:GEO)</v>
@@ -4481,7 +4469,7 @@
         <v>N</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="31" t="str">
         <f>Mom6m.Junk!A19</f>
         <v>United Airlines Holdings, Inc. (NASDAQGS:UAL)</v>
@@ -4518,7 +4506,7 @@
         <v>Y</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="31" t="str">
         <f>Mom6m.Junk!A20</f>
         <v>Comstock Resources, Inc. (NYSE:CRK)</v>
@@ -4555,7 +4543,7 @@
         <v>N</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="31" t="str">
         <f>Mom6m.Junk!A21</f>
         <v>Coinbase Global, Inc. (NASDAQGS:COIN)</v>
@@ -4592,7 +4580,7 @@
         <v>Y</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="31" t="str">
         <f>Mom6m.Junk!A22</f>
         <v>VEON Ltd. (NASDAQCM:VEON)</v>
@@ -4629,7 +4617,7 @@
         <v>N</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="31" t="str">
         <f>Mom6m.Junk!A23</f>
         <v>Coherent Corp. (NYSE:COHR)</v>
@@ -4666,7 +4654,7 @@
         <v>N</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="31" t="str">
         <f>Mom6m.Junk!A24</f>
         <v>Construction Partners, Inc. (NASDAQGS:ROAD)</v>
@@ -4703,7 +4691,7 @@
         <v>Y</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="31" t="str">
         <f>Mom6m.Junk!A25</f>
         <v>Bread Financial Holdings, Inc. (NYSE:BFH)</v>
@@ -4740,7 +4728,7 @@
         <v>N</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="31" t="str">
         <f>Mom6m.Junk!A26</f>
         <v>NRG Energy, Inc. (NYSE:NRG)</v>
@@ -4777,7 +4765,7 @@
         <v>N</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="31" t="str">
         <f>Mom6m.Junk!A27</f>
         <v>Cinemark Holdings, Inc. (NYSE:CNK)</v>
@@ -4814,7 +4802,7 @@
         <v>N</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="31" t="str">
         <f>Mom6m.Junk!A28</f>
         <v>Nebius Group N.V. (NASDAQGS:NBIS)</v>
@@ -4851,7 +4839,7 @@
         <v>N</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="31" t="str">
         <f>Mom6m.Junk!A29</f>
         <v>DT Midstream, Inc. (NYSE:DTM)</v>
@@ -4888,7 +4876,7 @@
         <v>N</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="31" t="str">
         <f>Mom6m.Junk!A30</f>
         <v>Telephone and Data Systems, Inc. (NYSE:TDS)</v>
@@ -4925,7 +4913,7 @@
         <v>Y</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="31" t="str">
         <f>Mom6m.Junk!A31</f>
         <v>Kratos Defense &amp; Security Solutions, Inc. (NASDAQGS:KTOS)</v>
@@ -4962,7 +4950,7 @@
         <v>N</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="31" t="str">
         <f>Mom6m.Junk!A32</f>
         <v>Kinetik Holdings Inc. (NYSE:KNTK)</v>
@@ -4999,7 +4987,7 @@
         <v>N</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="31" t="str">
         <f>Mom6m.Junk!A33</f>
         <v>Victory Capital Holdings, Inc. (NASDAQGS:VCTR)</v>
@@ -5036,7 +5024,7 @@
         <v>N</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="31" t="str">
         <f>Mom6m.Junk!A34</f>
         <v>GameStop Corp. (NYSE:GME)</v>
@@ -5073,7 +5061,7 @@
         <v>N</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="31" t="str">
         <f>Mom6m.Junk!A35</f>
         <v>Sportradar Group AG (NASDAQGS:SRAD)</v>
@@ -5110,7 +5098,7 @@
         <v>N</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="31" t="str">
         <f>Mom6m.Junk!A36</f>
         <v>Leonardo DRS, Inc. (NASDAQGS:DRS)</v>
@@ -5147,7 +5135,7 @@
         <v>N</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="31" t="str">
         <f>Mom6m.Junk!A37</f>
         <v>StepStone Group Inc. (NASDAQGS:STEP)</v>
@@ -5184,7 +5172,7 @@
         <v>N</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="31" t="str">
         <f>Mom6m.Junk!A38</f>
         <v>Mirion Technologies, Inc. (NYSE:MIR)</v>
@@ -5221,7 +5209,7 @@
         <v>N</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="31" t="str">
         <f>Mom6m.Junk!A39</f>
         <v>Royal Caribbean Cruises Ltd. (NYSE:RCL)</v>
@@ -5258,7 +5246,7 @@
         <v>N</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="31" t="str">
         <f>Mom6m.Junk!A40</f>
         <v>Alaska Air Group, Inc. (NYSE:ALK)</v>
@@ -5295,7 +5283,7 @@
         <v>Y</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="31" t="str">
         <f>Mom6m.Junk!A41</f>
         <v>Archrock, Inc. (NYSE:AROC)</v>
@@ -5332,7 +5320,7 @@
         <v>N</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="31" t="str">
         <f>Mom6m.Junk!A42</f>
         <v>EchoStar Corporation (NASDAQGS:SATS)</v>
@@ -5369,7 +5357,7 @@
         <v>N</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="31" t="str">
         <f>Mom6m.Junk!A43</f>
         <v>Lantheus Holdings, Inc. (NASDAQGM:LNTH)</v>
@@ -5406,7 +5394,7 @@
         <v>N</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="31" t="str">
         <f>Mom6m.Junk!A44</f>
         <v>Nu Holdings Ltd. (NYSE:NU)</v>
@@ -5443,7 +5431,7 @@
         <v>Y</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="31">
         <f>Mom6m.Junk!A45</f>
         <v>0</v>
@@ -5480,7 +5468,7 @@
         <v>N</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="31">
         <f>Mom6m.Junk!A46</f>
         <v>0</v>
@@ -5517,7 +5505,7 @@
         <v>N</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="31">
         <f>Mom6m.Junk!A47</f>
         <v>0</v>
@@ -5554,7 +5542,7 @@
         <v>N</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="31">
         <f>Mom6m.Junk!A48</f>
         <v>0</v>
@@ -5577,7 +5565,7 @@
       <c r="I41" s="33"/>
       <c r="J41" s="33"/>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="31">
         <f>Mom6m.Junk!A49</f>
         <v>0</v>
@@ -5600,7 +5588,7 @@
       <c r="I42" s="33"/>
       <c r="J42" s="33"/>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="31">
         <f>Mom6m.Junk!A50</f>
         <v>0</v>
@@ -5623,7 +5611,7 @@
       <c r="I43" s="33"/>
       <c r="J43" s="33"/>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="31">
         <f>Mom6m.Junk!A51</f>
         <v>0</v>
@@ -5646,7 +5634,7 @@
       <c r="I44" s="33"/>
       <c r="J44" s="33"/>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="31">
         <f>Mom6m.Junk!A52</f>
         <v>0</v>
@@ -5669,7 +5657,7 @@
       <c r="I45" s="33"/>
       <c r="J45" s="33"/>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="31">
         <f>Mom6m.Junk!A53</f>
         <v>0</v>
@@ -5692,7 +5680,7 @@
       <c r="I46" s="33"/>
       <c r="J46" s="33"/>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="31">
         <f>Mom6m.Junk!A54</f>
         <v>0</v>
@@ -5715,7 +5703,7 @@
       <c r="I47" s="33"/>
       <c r="J47" s="33"/>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="31">
         <f>Mom6m.Junk!A55</f>
         <v>0</v>
@@ -5738,7 +5726,7 @@
       <c r="I48" s="33"/>
       <c r="J48" s="33"/>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="31">
         <f>Mom6m.Junk!A56</f>
         <v>0</v>
@@ -5761,7 +5749,7 @@
       <c r="I49" s="33"/>
       <c r="J49" s="33"/>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="31">
         <f>Mom6m.Junk!A57</f>
         <v>0</v>
@@ -5784,7 +5772,7 @@
       <c r="I50" s="33"/>
       <c r="J50" s="33"/>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="31">
         <f>Mom6m.Junk!A58</f>
         <v>0</v>
@@ -5807,7 +5795,7 @@
       <c r="I51" s="33"/>
       <c r="J51" s="33"/>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="31">
         <f>Mom6m.Junk!A59</f>
         <v>0</v>
@@ -5830,7 +5818,7 @@
       <c r="I52" s="33"/>
       <c r="J52" s="33"/>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="31">
         <f>Mom6m.Junk!A60</f>
         <v>0</v>
@@ -5853,7 +5841,7 @@
       <c r="I53" s="33"/>
       <c r="J53" s="33"/>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" s="31">
         <f>Mom6m.Junk!A61</f>
         <v>0</v>
@@ -5876,7 +5864,7 @@
       <c r="I54" s="33"/>
       <c r="J54" s="33"/>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" s="31">
         <f>Mom6m.Junk!A62</f>
         <v>0</v>
@@ -5899,7 +5887,7 @@
       <c r="I55" s="33"/>
       <c r="J55" s="33"/>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="31">
         <f>Mom6m.Junk!A63</f>
         <v>0</v>
@@ -5922,7 +5910,7 @@
       <c r="I56" s="33"/>
       <c r="J56" s="33"/>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="31">
         <f>Mom6m.Junk!A64</f>
         <v>0</v>
@@ -5945,7 +5933,7 @@
       <c r="I57" s="33"/>
       <c r="J57" s="33"/>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" s="31">
         <f>Mom6m.Junk!A65</f>
         <v>0</v>
@@ -5968,7 +5956,7 @@
       <c r="I58" s="33"/>
       <c r="J58" s="33"/>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" s="31">
         <f>Mom6m.Junk!A66</f>
         <v>0</v>
@@ -5991,7 +5979,7 @@
       <c r="I59" s="33"/>
       <c r="J59" s="33"/>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" s="31">
         <f>Mom6m.Junk!A67</f>
         <v>0</v>
@@ -6014,7 +6002,7 @@
       <c r="I60" s="33"/>
       <c r="J60" s="33"/>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" s="31">
         <f>Mom6m.Junk!A68</f>
         <v>0</v>
@@ -6037,7 +6025,7 @@
       <c r="I61" s="33"/>
       <c r="J61" s="33"/>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" s="31">
         <f>Mom6m.Junk!A69</f>
         <v>0</v>
@@ -6060,7 +6048,7 @@
       <c r="I62" s="33"/>
       <c r="J62" s="33"/>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" s="31">
         <f>Mom6m.Junk!A70</f>
         <v>0</v>
@@ -6083,7 +6071,7 @@
       <c r="I63" s="33"/>
       <c r="J63" s="33"/>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" s="31">
         <f>Mom6m.Junk!A71</f>
         <v>0</v>
@@ -6106,7 +6094,7 @@
       <c r="I64" s="33"/>
       <c r="J64" s="33"/>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" s="31">
         <f>Mom6m.Junk!A72</f>
         <v>0</v>
@@ -6129,7 +6117,7 @@
       <c r="I65" s="33"/>
       <c r="J65" s="33"/>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" s="31">
         <f>Mom6m.Junk!A73</f>
         <v>0</v>
@@ -6152,7 +6140,7 @@
       <c r="I66" s="33"/>
       <c r="J66" s="33"/>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" s="31">
         <f>Mom6m.Junk!A74</f>
         <v>0</v>
@@ -6175,7 +6163,7 @@
       <c r="I67" s="33"/>
       <c r="J67" s="33"/>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" s="31">
         <f>Mom6m.Junk!A75</f>
         <v>0</v>
@@ -6198,7 +6186,7 @@
       <c r="I68" s="33"/>
       <c r="J68" s="33"/>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" s="31">
         <f>Mom6m.Junk!A76</f>
         <v>0</v>
@@ -6221,7 +6209,7 @@
       <c r="I69" s="33"/>
       <c r="J69" s="33"/>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" s="31">
         <f>Mom6m.Junk!A77</f>
         <v>0</v>
@@ -6244,7 +6232,7 @@
       <c r="I70" s="33"/>
       <c r="J70" s="33"/>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" s="31">
         <f>Mom6m.Junk!A78</f>
         <v>0</v>
@@ -6267,7 +6255,7 @@
       <c r="I71" s="33"/>
       <c r="J71" s="33"/>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" s="31">
         <f>Mom6m.Junk!A79</f>
         <v>0</v>
@@ -6290,7 +6278,7 @@
       <c r="I72" s="33"/>
       <c r="J72" s="33"/>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" s="31">
         <f>Mom6m.Junk!A80</f>
         <v>0</v>
@@ -6313,7 +6301,7 @@
       <c r="I73" s="33"/>
       <c r="J73" s="33"/>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" s="31">
         <f>Mom6m.Junk!A81</f>
         <v>0</v>
@@ -6336,7 +6324,7 @@
       <c r="I74" s="33"/>
       <c r="J74" s="33"/>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" s="31">
         <f>Mom6m.Junk!A82</f>
         <v>0</v>
@@ -6359,7 +6347,7 @@
       <c r="I75" s="33"/>
       <c r="J75" s="33"/>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" s="31">
         <f>Mom6m.Junk!A83</f>
         <v>0</v>
@@ -6382,7 +6370,7 @@
       <c r="I76" s="33"/>
       <c r="J76" s="33"/>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" s="31">
         <f>Mom6m.Junk!A84</f>
         <v>0</v>
@@ -6405,7 +6393,7 @@
       <c r="I77" s="33"/>
       <c r="J77" s="33"/>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" s="31">
         <f>Mom6m.Junk!A85</f>
         <v>0</v>
@@ -6428,7 +6416,7 @@
       <c r="I78" s="33"/>
       <c r="J78" s="33"/>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" s="31">
         <f>Mom6m.Junk!A86</f>
         <v>0</v>
@@ -6451,7 +6439,7 @@
       <c r="I79" s="33"/>
       <c r="J79" s="33"/>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" s="31">
         <f>Mom6m.Junk!A87</f>
         <v>0</v>
@@ -6474,7 +6462,7 @@
       <c r="I80" s="33"/>
       <c r="J80" s="33"/>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" s="31">
         <f>Mom6m.Junk!A88</f>
         <v>0</v>
@@ -6497,7 +6485,7 @@
       <c r="I81" s="33"/>
       <c r="J81" s="33"/>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" s="31">
         <f>Mom6m.Junk!A89</f>
         <v>0</v>
@@ -6520,7 +6508,7 @@
       <c r="I82" s="33"/>
       <c r="J82" s="33"/>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83" s="31">
         <f>Mom6m.Junk!A90</f>
         <v>0</v>
@@ -6543,7 +6531,7 @@
       <c r="I83" s="33"/>
       <c r="J83" s="33"/>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" s="31">
         <f>Mom6m.Junk!A91</f>
         <v>0</v>
@@ -6566,7 +6554,7 @@
       <c r="I84" s="33"/>
       <c r="J84" s="33"/>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" s="31">
         <f>Mom6m.Junk!A92</f>
         <v>0</v>
@@ -6589,7 +6577,7 @@
       <c r="I85" s="33"/>
       <c r="J85" s="33"/>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86" s="31">
         <f>Mom6m.Junk!A93</f>
         <v>0</v>
@@ -6612,7 +6600,7 @@
       <c r="I86" s="33"/>
       <c r="J86" s="33"/>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87" s="31">
         <f>Mom6m.Junk!A94</f>
         <v>0</v>
@@ -6635,7 +6623,7 @@
       <c r="I87" s="33"/>
       <c r="J87" s="33"/>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A88" s="31">
         <f>Mom6m.Junk!A95</f>
         <v>0</v>
@@ -6658,7 +6646,7 @@
       <c r="I88" s="33"/>
       <c r="J88" s="33"/>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A89" s="31">
         <f>Mom6m.Junk!A96</f>
         <v>0</v>
@@ -6681,7 +6669,7 @@
       <c r="I89" s="33"/>
       <c r="J89" s="33"/>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A90" s="31">
         <f>Mom6m.Junk!A97</f>
         <v>0</v>
@@ -6704,7 +6692,7 @@
       <c r="I90" s="33"/>
       <c r="J90" s="33"/>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91" s="31">
         <f>Mom6m.Junk!A98</f>
         <v>0</v>
@@ -6727,7 +6715,7 @@
       <c r="I91" s="33"/>
       <c r="J91" s="33"/>
     </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92" s="31">
         <f>Mom6m.Junk!A99</f>
         <v>0</v>
@@ -6750,7 +6738,7 @@
       <c r="I92" s="33"/>
       <c r="J92" s="33"/>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A93" s="31">
         <f>Mom6m.Junk!A100</f>
         <v>0</v>
@@ -6773,7 +6761,7 @@
       <c r="I93" s="33"/>
       <c r="J93" s="33"/>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A94" s="31">
         <f>Mom6m.Junk!A101</f>
         <v>0</v>
@@ -6796,7 +6784,7 @@
       <c r="I94" s="33"/>
       <c r="J94" s="33"/>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95" s="31">
         <f>Mom6m.Junk!A102</f>
         <v>0</v>
@@ -6819,7 +6807,7 @@
       <c r="I95" s="33"/>
       <c r="J95" s="33"/>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A96" s="31">
         <f>Mom6m.Junk!A103</f>
         <v>0</v>
@@ -6842,7 +6830,7 @@
       <c r="I96" s="33"/>
       <c r="J96" s="33"/>
     </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A97" s="31">
         <f>Mom6m.Junk!A104</f>
         <v>0</v>
@@ -6865,7 +6853,7 @@
       <c r="I97" s="33"/>
       <c r="J97" s="33"/>
     </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A98" s="31">
         <f>Mom6m.Junk!A105</f>
         <v>0</v>
@@ -6888,7 +6876,7 @@
       <c r="I98" s="33"/>
       <c r="J98" s="33"/>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A99" s="31">
         <f>Mom6m.Junk!A106</f>
         <v>0</v>
@@ -6911,7 +6899,7 @@
       <c r="I99" s="33"/>
       <c r="J99" s="33"/>
     </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A100" s="31">
         <f>Mom6m.Junk!A107</f>
         <v>0</v>
@@ -6934,7 +6922,7 @@
       <c r="I100" s="33"/>
       <c r="J100" s="33"/>
     </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A101" s="31">
         <f>Mom6m.Junk!A108</f>
         <v>0</v>
@@ -6957,7 +6945,7 @@
       <c r="I101" s="33"/>
       <c r="J101" s="33"/>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A102" s="31">
         <f>Mom6m.Junk!A109</f>
         <v>0</v>
@@ -6980,7 +6968,7 @@
       <c r="I102" s="33"/>
       <c r="J102" s="33"/>
     </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A103" s="31">
         <f>Mom6m.Junk!A110</f>
         <v>0</v>
@@ -7003,7 +6991,7 @@
       <c r="I103" s="33"/>
       <c r="J103" s="33"/>
     </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A104" s="31">
         <f>Mom6m.Junk!A111</f>
         <v>0</v>
@@ -7026,7 +7014,7 @@
       <c r="I104" s="33"/>
       <c r="J104" s="33"/>
     </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A105" s="31">
         <f>Mom6m.Junk!A112</f>
         <v>0</v>
@@ -7049,7 +7037,7 @@
       <c r="I105" s="33"/>
       <c r="J105" s="33"/>
     </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A106" s="31">
         <f>Mom6m.Junk!A113</f>
         <v>0</v>
@@ -7072,7 +7060,7 @@
       <c r="I106" s="33"/>
       <c r="J106" s="33"/>
     </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A107" s="31">
         <f>Mom6m.Junk!A114</f>
         <v>0</v>
@@ -7095,7 +7083,7 @@
       <c r="I107" s="33"/>
       <c r="J107" s="33"/>
     </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A108" s="31">
         <f>Mom6m.Junk!A115</f>
         <v>0</v>
@@ -7118,7 +7106,7 @@
       <c r="I108" s="33"/>
       <c r="J108" s="33"/>
     </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A109" s="31">
         <f>Mom6m.Junk!A116</f>
         <v>0</v>
@@ -7141,7 +7129,7 @@
       <c r="I109" s="33"/>
       <c r="J109" s="33"/>
     </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A110" s="31">
         <f>Mom6m.Junk!A117</f>
         <v>0</v>
@@ -7164,7 +7152,7 @@
       <c r="I110" s="33"/>
       <c r="J110" s="33"/>
     </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A111" s="31">
         <f>Mom6m.Junk!A118</f>
         <v>0</v>
@@ -7187,7 +7175,7 @@
       <c r="I111" s="33"/>
       <c r="J111" s="33"/>
     </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A112" s="31">
         <f>Mom6m.Junk!A119</f>
         <v>0</v>
@@ -7210,7 +7198,7 @@
       <c r="I112" s="33"/>
       <c r="J112" s="33"/>
     </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A113" s="31">
         <f>Mom6m.Junk!A120</f>
         <v>0</v>
@@ -7233,7 +7221,7 @@
       <c r="I113" s="33"/>
       <c r="J113" s="33"/>
     </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A114" s="31">
         <f>Mom6m.Junk!A121</f>
         <v>0</v>
@@ -7256,7 +7244,7 @@
       <c r="I114" s="33"/>
       <c r="J114" s="33"/>
     </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A115" s="31">
         <f>Mom6m.Junk!A122</f>
         <v>0</v>
@@ -7279,7 +7267,7 @@
       <c r="I115" s="33"/>
       <c r="J115" s="33"/>
     </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A116" s="31">
         <f>Mom6m.Junk!A123</f>
         <v>0</v>
@@ -7302,7 +7290,7 @@
       <c r="I116" s="33"/>
       <c r="J116" s="33"/>
     </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A117" s="31">
         <f>Mom6m.Junk!A124</f>
         <v>0</v>
@@ -7325,7 +7313,7 @@
       <c r="I117" s="33"/>
       <c r="J117" s="33"/>
     </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A118" s="31">
         <f>Mom6m.Junk!A125</f>
         <v>0</v>
@@ -7348,7 +7336,7 @@
       <c r="I118" s="33"/>
       <c r="J118" s="33"/>
     </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A119" s="31">
         <f>Mom6m.Junk!A126</f>
         <v>0</v>
@@ -7371,7 +7359,7 @@
       <c r="I119" s="33"/>
       <c r="J119" s="33"/>
     </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A120" s="31">
         <f>Mom6m.Junk!A127</f>
         <v>0</v>
@@ -7394,7 +7382,7 @@
       <c r="I120" s="33"/>
       <c r="J120" s="33"/>
     </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A121" s="31">
         <f>Mom6m.Junk!A128</f>
         <v>0</v>
@@ -7417,7 +7405,7 @@
       <c r="I121" s="33"/>
       <c r="J121" s="33"/>
     </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A122" s="31">
         <f>Mom6m.Junk!A129</f>
         <v>0</v>
@@ -7440,7 +7428,7 @@
       <c r="I122" s="33"/>
       <c r="J122" s="33"/>
     </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A123" s="31">
         <f>Mom6m.Junk!A130</f>
         <v>0</v>
@@ -7463,7 +7451,7 @@
       <c r="I123" s="33"/>
       <c r="J123" s="33"/>
     </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A124" s="31">
         <f>Mom6m.Junk!A131</f>
         <v>0</v>
@@ -7486,7 +7474,7 @@
       <c r="I124" s="33"/>
       <c r="J124" s="33"/>
     </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A125" s="31">
         <f>Mom6m.Junk!A132</f>
         <v>0</v>
@@ -7509,7 +7497,7 @@
       <c r="I125" s="33"/>
       <c r="J125" s="33"/>
     </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A126" s="31">
         <f>Mom6m.Junk!A133</f>
         <v>0</v>
@@ -7532,7 +7520,7 @@
       <c r="I126" s="33"/>
       <c r="J126" s="33"/>
     </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A127" s="31">
         <f>Mom6m.Junk!A134</f>
         <v>0</v>
@@ -7555,7 +7543,7 @@
       <c r="I127" s="33"/>
       <c r="J127" s="33"/>
     </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A128" s="31">
         <f>Mom6m.Junk!A135</f>
         <v>0</v>
@@ -7578,7 +7566,7 @@
       <c r="I128" s="33"/>
       <c r="J128" s="33"/>
     </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A129" s="31">
         <f>Mom6m.Junk!A136</f>
         <v>0</v>
@@ -7601,7 +7589,7 @@
       <c r="I129" s="33"/>
       <c r="J129" s="33"/>
     </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A130" s="31">
         <f>Mom6m.Junk!A137</f>
         <v>0</v>
@@ -7624,7 +7612,7 @@
       <c r="I130" s="33"/>
       <c r="J130" s="33"/>
     </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A131" s="31">
         <f>Mom6m.Junk!A138</f>
         <v>0</v>
@@ -7647,7 +7635,7 @@
       <c r="I131" s="33"/>
       <c r="J131" s="33"/>
     </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A132" s="31">
         <f>Mom6m.Junk!A139</f>
         <v>0</v>
@@ -7670,7 +7658,7 @@
       <c r="I132" s="33"/>
       <c r="J132" s="33"/>
     </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="133" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A133" s="31">
         <f>Mom6m.Junk!A140</f>
         <v>0</v>
@@ -7693,7 +7681,7 @@
       <c r="I133" s="33"/>
       <c r="J133" s="33"/>
     </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="134" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A134" s="31">
         <f>Mom6m.Junk!A141</f>
         <v>0</v>
@@ -7716,7 +7704,7 @@
       <c r="I134" s="33"/>
       <c r="J134" s="33"/>
     </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="135" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A135" s="31">
         <f>Mom6m.Junk!A142</f>
         <v>0</v>
@@ -7727,7 +7715,7 @@
       <c r="I135" s="33"/>
       <c r="J135" s="33"/>
     </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="136" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A136" s="31">
         <f>Mom6m.Junk!A143</f>
         <v>0</v>
@@ -7738,7 +7726,7 @@
       <c r="I136" s="33"/>
       <c r="J136" s="33"/>
     </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="137" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A137" s="31">
         <f>Mom6m.Junk!A144</f>
         <v>0</v>
@@ -7749,7 +7737,7 @@
       <c r="I137" s="33"/>
       <c r="J137" s="33"/>
     </row>
-    <row r="138" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="138" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A138" s="31">
         <f>Mom6m.Junk!A145</f>
         <v>0</v>
@@ -7760,521 +7748,521 @@
       <c r="I138" s="33"/>
       <c r="J138" s="33"/>
     </row>
-    <row r="139" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="139" spans="1:10" x14ac:dyDescent="0.25">
       <c r="F139" s="14"/>
       <c r="G139" s="33"/>
       <c r="H139" s="33"/>
       <c r="I139" s="33"/>
       <c r="J139" s="33"/>
     </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="140" spans="1:10" x14ac:dyDescent="0.25">
       <c r="F140" s="14"/>
       <c r="G140" s="33"/>
       <c r="H140" s="33"/>
       <c r="I140" s="33"/>
       <c r="J140" s="33"/>
     </row>
-    <row r="141" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="141" spans="1:10" x14ac:dyDescent="0.25">
       <c r="F141" s="14"/>
       <c r="G141" s="33"/>
       <c r="H141" s="33"/>
       <c r="I141" s="33"/>
       <c r="J141" s="33"/>
     </row>
-    <row r="142" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="142" spans="1:10" x14ac:dyDescent="0.25">
       <c r="F142" s="14"/>
       <c r="G142" s="33"/>
       <c r="H142" s="33"/>
       <c r="I142" s="33"/>
       <c r="J142" s="33"/>
     </row>
-    <row r="143" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="143" spans="1:10" x14ac:dyDescent="0.25">
       <c r="F143" s="14"/>
       <c r="G143" s="33"/>
       <c r="H143" s="33"/>
       <c r="I143" s="33"/>
       <c r="J143" s="33"/>
     </row>
-    <row r="144" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="144" spans="1:10" x14ac:dyDescent="0.25">
       <c r="F144" s="14"/>
       <c r="G144" s="33"/>
       <c r="H144" s="33"/>
       <c r="I144" s="33"/>
       <c r="J144" s="33"/>
     </row>
-    <row r="145" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="145" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F145" s="14"/>
       <c r="G145" s="33"/>
       <c r="H145" s="33"/>
       <c r="I145" s="33"/>
       <c r="J145" s="33"/>
     </row>
-    <row r="146" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="146" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F146" s="14"/>
       <c r="G146" s="33"/>
       <c r="H146" s="33"/>
       <c r="I146" s="33"/>
       <c r="J146" s="33"/>
     </row>
-    <row r="147" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="147" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F147" s="14"/>
       <c r="G147" s="33"/>
       <c r="H147" s="33"/>
       <c r="I147" s="33"/>
       <c r="J147" s="33"/>
     </row>
-    <row r="148" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="148" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F148" s="14"/>
       <c r="G148" s="33"/>
       <c r="H148" s="33"/>
       <c r="I148" s="33"/>
       <c r="J148" s="33"/>
     </row>
-    <row r="149" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="149" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F149" s="14"/>
       <c r="G149" s="33"/>
       <c r="H149" s="33"/>
       <c r="I149" s="33"/>
       <c r="J149" s="33"/>
     </row>
-    <row r="150" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="150" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F150" s="14"/>
       <c r="G150" s="33"/>
       <c r="H150" s="33"/>
       <c r="I150" s="33"/>
       <c r="J150" s="33"/>
     </row>
-    <row r="151" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="151" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F151" s="14"/>
       <c r="G151" s="33"/>
       <c r="H151" s="33"/>
       <c r="I151" s="33"/>
       <c r="J151" s="33"/>
     </row>
-    <row r="152" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="152" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F152" s="14"/>
       <c r="G152" s="33"/>
       <c r="H152" s="33"/>
       <c r="I152" s="33"/>
       <c r="J152" s="33"/>
     </row>
-    <row r="153" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="153" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F153" s="14"/>
       <c r="G153" s="33"/>
       <c r="H153" s="33"/>
       <c r="I153" s="33"/>
       <c r="J153" s="33"/>
     </row>
-    <row r="154" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="154" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F154" s="14"/>
       <c r="G154" s="33"/>
       <c r="H154" s="33"/>
       <c r="I154" s="33"/>
       <c r="J154" s="33"/>
     </row>
-    <row r="155" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="155" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F155" s="14"/>
       <c r="G155" s="33"/>
       <c r="H155" s="33"/>
       <c r="I155" s="33"/>
       <c r="J155" s="33"/>
     </row>
-    <row r="156" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="156" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F156" s="14"/>
       <c r="G156" s="33"/>
       <c r="H156" s="33"/>
       <c r="I156" s="33"/>
       <c r="J156" s="33"/>
     </row>
-    <row r="157" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="157" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F157" s="14"/>
       <c r="G157" s="33"/>
       <c r="H157" s="33"/>
       <c r="I157" s="33"/>
       <c r="J157" s="33"/>
     </row>
-    <row r="158" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="158" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F158" s="14"/>
       <c r="G158" s="33"/>
       <c r="H158" s="33"/>
       <c r="I158" s="33"/>
       <c r="J158" s="33"/>
     </row>
-    <row r="159" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="159" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F159" s="14"/>
       <c r="G159" s="33"/>
       <c r="H159" s="33"/>
       <c r="I159" s="33"/>
       <c r="J159" s="33"/>
     </row>
-    <row r="160" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="160" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F160" s="14"/>
       <c r="G160" s="33"/>
       <c r="H160" s="33"/>
       <c r="I160" s="33"/>
       <c r="J160" s="33"/>
     </row>
-    <row r="161" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="161" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F161" s="14"/>
       <c r="G161" s="33"/>
       <c r="H161" s="33"/>
       <c r="I161" s="33"/>
       <c r="J161" s="33"/>
     </row>
-    <row r="162" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="162" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F162" s="14"/>
       <c r="G162" s="33"/>
       <c r="H162" s="33"/>
       <c r="I162" s="33"/>
       <c r="J162" s="33"/>
     </row>
-    <row r="163" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="163" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F163" s="14"/>
       <c r="G163" s="33"/>
       <c r="H163" s="33"/>
       <c r="I163" s="33"/>
       <c r="J163" s="33"/>
     </row>
-    <row r="164" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="164" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F164" s="14"/>
       <c r="G164" s="33"/>
       <c r="H164" s="33"/>
       <c r="I164" s="33"/>
       <c r="J164" s="33"/>
     </row>
-    <row r="165" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="165" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F165" s="14"/>
       <c r="G165" s="33"/>
       <c r="H165" s="33"/>
       <c r="I165" s="33"/>
       <c r="J165" s="33"/>
     </row>
-    <row r="166" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="166" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F166" s="14"/>
       <c r="G166" s="33"/>
       <c r="H166" s="33"/>
       <c r="I166" s="33"/>
       <c r="J166" s="33"/>
     </row>
-    <row r="167" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="167" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F167" s="14"/>
       <c r="G167" s="33"/>
       <c r="H167" s="33"/>
       <c r="I167" s="33"/>
       <c r="J167" s="33"/>
     </row>
-    <row r="168" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="168" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F168" s="14"/>
       <c r="G168" s="33"/>
       <c r="H168" s="33"/>
       <c r="I168" s="33"/>
       <c r="J168" s="33"/>
     </row>
-    <row r="169" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="169" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F169" s="14"/>
       <c r="G169" s="33"/>
       <c r="H169" s="33"/>
       <c r="I169" s="33"/>
       <c r="J169" s="33"/>
     </row>
-    <row r="170" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="170" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F170" s="14"/>
       <c r="G170" s="33"/>
       <c r="H170" s="33"/>
       <c r="I170" s="33"/>
       <c r="J170" s="33"/>
     </row>
-    <row r="171" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="171" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F171" s="14"/>
       <c r="G171" s="33"/>
       <c r="H171" s="33"/>
       <c r="I171" s="33"/>
       <c r="J171" s="33"/>
     </row>
-    <row r="172" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="172" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F172" s="14"/>
       <c r="G172" s="33"/>
       <c r="H172" s="33"/>
       <c r="I172" s="33"/>
       <c r="J172" s="33"/>
     </row>
-    <row r="173" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="173" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F173" s="14"/>
       <c r="G173" s="33"/>
       <c r="H173" s="33"/>
       <c r="I173" s="33"/>
       <c r="J173" s="33"/>
     </row>
-    <row r="174" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="174" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F174" s="14"/>
       <c r="G174" s="33"/>
       <c r="H174" s="33"/>
       <c r="I174" s="33"/>
       <c r="J174" s="33"/>
     </row>
-    <row r="175" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="175" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F175" s="14"/>
       <c r="G175" s="33"/>
       <c r="H175" s="33"/>
       <c r="I175" s="33"/>
       <c r="J175" s="33"/>
     </row>
-    <row r="176" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="176" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F176" s="14"/>
       <c r="G176" s="33"/>
       <c r="H176" s="33"/>
       <c r="I176" s="33"/>
       <c r="J176" s="33"/>
     </row>
-    <row r="177" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="177" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F177" s="14"/>
       <c r="G177" s="33"/>
       <c r="H177" s="33"/>
       <c r="I177" s="33"/>
       <c r="J177" s="33"/>
     </row>
-    <row r="178" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="178" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F178" s="14"/>
       <c r="G178" s="33"/>
       <c r="H178" s="33"/>
       <c r="I178" s="33"/>
       <c r="J178" s="33"/>
     </row>
-    <row r="179" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="179" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F179" s="14"/>
       <c r="G179" s="33"/>
       <c r="H179" s="33"/>
       <c r="I179" s="33"/>
       <c r="J179" s="33"/>
     </row>
-    <row r="180" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="180" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F180" s="14"/>
       <c r="G180" s="33"/>
       <c r="H180" s="33"/>
       <c r="I180" s="33"/>
       <c r="J180" s="33"/>
     </row>
-    <row r="181" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="181" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F181" s="14"/>
       <c r="G181" s="33"/>
       <c r="H181" s="33"/>
       <c r="I181" s="33"/>
       <c r="J181" s="33"/>
     </row>
-    <row r="182" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="182" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F182" s="14"/>
       <c r="G182" s="33"/>
       <c r="H182" s="33"/>
       <c r="I182" s="33"/>
       <c r="J182" s="33"/>
     </row>
-    <row r="183" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="183" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F183" s="14"/>
       <c r="G183" s="33"/>
       <c r="H183" s="33"/>
       <c r="I183" s="33"/>
       <c r="J183" s="33"/>
     </row>
-    <row r="184" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="184" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F184" s="14"/>
       <c r="G184" s="33"/>
       <c r="H184" s="33"/>
       <c r="I184" s="33"/>
       <c r="J184" s="33"/>
     </row>
-    <row r="185" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="185" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F185" s="14"/>
       <c r="G185" s="33"/>
       <c r="H185" s="33"/>
       <c r="I185" s="33"/>
       <c r="J185" s="33"/>
     </row>
-    <row r="186" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="186" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F186" s="14"/>
       <c r="G186" s="33"/>
       <c r="H186" s="33"/>
       <c r="I186" s="33"/>
       <c r="J186" s="33"/>
     </row>
-    <row r="187" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="187" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F187" s="14"/>
       <c r="G187" s="33"/>
       <c r="H187" s="33"/>
       <c r="I187" s="33"/>
       <c r="J187" s="33"/>
     </row>
-    <row r="188" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="188" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F188" s="14"/>
       <c r="G188" s="33"/>
       <c r="H188" s="33"/>
       <c r="I188" s="33"/>
       <c r="J188" s="33"/>
     </row>
-    <row r="189" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="189" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F189" s="14"/>
       <c r="G189" s="33"/>
       <c r="H189" s="33"/>
       <c r="I189" s="33"/>
       <c r="J189" s="33"/>
     </row>
-    <row r="190" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="190" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F190" s="14"/>
       <c r="G190" s="33"/>
       <c r="H190" s="33"/>
       <c r="I190" s="33"/>
       <c r="J190" s="33"/>
     </row>
-    <row r="191" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="191" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F191" s="14"/>
       <c r="G191" s="33"/>
       <c r="H191" s="33"/>
       <c r="I191" s="33"/>
       <c r="J191" s="33"/>
     </row>
-    <row r="192" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="192" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F192" s="14"/>
       <c r="G192" s="33"/>
       <c r="H192" s="33"/>
       <c r="I192" s="33"/>
       <c r="J192" s="33"/>
     </row>
-    <row r="193" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="193" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F193" s="14"/>
       <c r="G193" s="33"/>
       <c r="H193" s="33"/>
       <c r="I193" s="33"/>
       <c r="J193" s="33"/>
     </row>
-    <row r="194" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="194" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F194" s="14"/>
       <c r="G194" s="33"/>
       <c r="H194" s="33"/>
       <c r="I194" s="33"/>
       <c r="J194" s="33"/>
     </row>
-    <row r="195" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="195" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F195" s="14"/>
       <c r="G195" s="33"/>
       <c r="H195" s="33"/>
       <c r="I195" s="33"/>
       <c r="J195" s="33"/>
     </row>
-    <row r="196" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="196" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F196" s="14"/>
       <c r="G196" s="33"/>
       <c r="H196" s="33"/>
       <c r="I196" s="33"/>
       <c r="J196" s="33"/>
     </row>
-    <row r="197" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="197" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F197" s="14"/>
       <c r="G197" s="33"/>
       <c r="H197" s="33"/>
       <c r="I197" s="33"/>
       <c r="J197" s="33"/>
     </row>
-    <row r="198" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="198" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F198" s="14"/>
       <c r="G198" s="33"/>
       <c r="H198" s="33"/>
       <c r="I198" s="33"/>
       <c r="J198" s="33"/>
     </row>
-    <row r="199" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="199" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F199" s="14"/>
       <c r="G199" s="33"/>
       <c r="H199" s="33"/>
       <c r="I199" s="33"/>
       <c r="J199" s="33"/>
     </row>
-    <row r="200" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="200" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F200" s="14"/>
       <c r="G200" s="33"/>
       <c r="H200" s="33"/>
       <c r="I200" s="33"/>
       <c r="J200" s="33"/>
     </row>
-    <row r="201" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="201" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F201" s="14"/>
       <c r="G201" s="33"/>
       <c r="H201" s="33"/>
       <c r="I201" s="33"/>
       <c r="J201" s="33"/>
     </row>
-    <row r="202" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="202" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F202" s="14"/>
       <c r="G202" s="33"/>
       <c r="H202" s="33"/>
       <c r="I202" s="33"/>
       <c r="J202" s="33"/>
     </row>
-    <row r="203" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="203" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F203" s="14"/>
       <c r="G203" s="33"/>
       <c r="H203" s="33"/>
       <c r="I203" s="33"/>
       <c r="J203" s="33"/>
     </row>
-    <row r="204" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="204" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F204" s="14"/>
       <c r="G204" s="33"/>
       <c r="H204" s="33"/>
       <c r="I204" s="33"/>
       <c r="J204" s="33"/>
     </row>
-    <row r="205" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="205" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F205" s="14"/>
       <c r="G205" s="33"/>
       <c r="H205" s="33"/>
       <c r="I205" s="33"/>
       <c r="J205" s="33"/>
     </row>
-    <row r="206" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="206" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F206" s="14"/>
       <c r="G206" s="33"/>
       <c r="H206" s="33"/>
       <c r="I206" s="33"/>
       <c r="J206" s="33"/>
     </row>
-    <row r="207" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="207" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F207" s="14"/>
       <c r="G207" s="33"/>
       <c r="H207" s="33"/>
       <c r="I207" s="33"/>
       <c r="J207" s="33"/>
     </row>
-    <row r="208" spans="6:10" x14ac:dyDescent="0.45">
+    <row r="208" spans="6:10" x14ac:dyDescent="0.25">
       <c r="F208" s="14"/>
       <c r="G208" s="33"/>
       <c r="H208" s="33"/>
       <c r="I208" s="33"/>
       <c r="J208" s="33"/>
     </row>
-    <row r="209" spans="7:10" x14ac:dyDescent="0.45">
+    <row r="209" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G209" s="33"/>
       <c r="H209" s="33"/>
       <c r="I209" s="33"/>
       <c r="J209" s="33"/>
     </row>
-    <row r="210" spans="7:10" x14ac:dyDescent="0.45">
+    <row r="210" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G210" s="33"/>
       <c r="H210" s="33"/>
       <c r="I210" s="33"/>
       <c r="J210" s="33"/>
     </row>
-    <row r="211" spans="7:10" x14ac:dyDescent="0.45">
+    <row r="211" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G211" s="33"/>
       <c r="H211" s="33"/>
       <c r="I211" s="33"/>
       <c r="J211" s="33"/>
     </row>
-    <row r="212" spans="7:10" x14ac:dyDescent="0.45">
+    <row r="212" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G212" s="33"/>
       <c r="H212" s="33"/>
       <c r="I212" s="33"/>
       <c r="J212" s="33"/>
     </row>
-    <row r="213" spans="7:10" x14ac:dyDescent="0.45">
+    <row r="213" spans="7:10" x14ac:dyDescent="0.25">
       <c r="G213" s="33"/>
       <c r="H213" s="33"/>
       <c r="I213" s="33"/>
@@ -8298,71 +8286,71 @@
     <tabColor theme="9"/>
   </sheetPr>
   <dimension ref="A1:J88"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25" outlineLevelCol="1" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="45.46484375" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="19.46484375" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="4" max="4" width="19.46484375" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="19.46484375" style="1" hidden="1" customWidth="1"/>
-    <col min="6" max="7" width="19.46484375" style="16" customWidth="1"/>
-    <col min="8" max="9" width="19.46484375" style="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.86328125" style="1"/>
+    <col min="1" max="1" width="45.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="19.42578125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="4" max="4" width="19.42578125" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="19.42578125" style="1" hidden="1" customWidth="1"/>
+    <col min="6" max="7" width="19.42578125" style="16" customWidth="1"/>
+    <col min="8" max="9" width="19.42578125" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="F1" s="15"/>
       <c r="G1" s="15"/>
     </row>
-    <row r="2" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>66</v>
       </c>
       <c r="F2" s="15"/>
       <c r="G2" s="15"/>
     </row>
-    <row r="3" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="F3" s="15"/>
       <c r="G3" s="15"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="str">
         <f>_xll.SNL.Clients.Office.Excel.Functions.SPGTable($B$9:$B$43,$C$6:$I$6,,"Options:Curr=USD,Mag=Standard,ConvMethod=R,FilingVer=Current/Restated")</f>
         <v>SPGTable</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A5" s="35" t="str">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="11" t="str">
         <f>_xll.SNL.Clients.Office.Excel.Functions.SPGLabel(266637,"SP_ENTITY_NAME","","","Options:Curr=USD,Mag=Standard,ConvMethod=R,FilingVer=Current/Restated")</f>
         <v>Entity Name</v>
       </c>
-      <c r="B5" s="36" t="str">
+      <c r="B5" s="6" t="str">
         <f>_xll.SNL.Clients.Office.Excel.Functions.SPGLabel(266637,"SP_ENTITY_ID","","","Options:Curr=USD,Mag=Standard,ConvMethod=R,FilingVer=Current/Restated")</f>
         <v>Entity ID</v>
       </c>
-      <c r="C5" s="36" t="str">
+      <c r="C5" s="6" t="str">
         <f>_xll.SNL.Clients.Office.Excel.Functions.SPGLabel(266637,"SP_EXCHANGE","","","Options:Curr=USD,Mag=Standard,ConvMethod=R,FilingVer=Current/Restated")</f>
         <v>Exchange</v>
       </c>
-      <c r="D5" s="36" t="str">
+      <c r="D5" s="6" t="str">
         <f>_xll.SNL.Clients.Office.Excel.Functions.SPGLabel(266637,"SP_MARKETCAP","","","Options:Curr=USD,Mag=Standard,ConvMethod=R,FilingVer=Current/Restated")</f>
         <v>Market Capitalization ($M)</v>
       </c>
-      <c r="E5" s="36" t="str">
+      <c r="E5" s="6" t="str">
         <f>_xll.SNL.Clients.Office.Excel.Functions.SPGLabel(266637,"SP_PRICE_CLOSE","","","Options:Curr=USD,Mag=Standard,ConvMethod=R,FilingVer=Current/Restated")</f>
         <v>Day Close Price ($)</v>
       </c>
-      <c r="F5" s="36" t="str">
+      <c r="F5" s="6" t="str">
         <f>_xll.SNL.Clients.Office.Excel.Functions.SPGLabel(266637,"RD_CREDIT_RATING_GLOBAL","Issuer Credit Rating","Local Currency LT|Current","Options:Curr=USD,Mag=Standard,ConvMethod=R,FilingVer=Current/Restated")</f>
         <v>S&amp;P Credit Rating</v>
       </c>
-      <c r="G5" s="36" t="str">
+      <c r="G5" s="6" t="str">
         <f>_xll.SNL.Clients.Office.Excel.Functions.SPGLabel(266637,"SP_PRICE_CHANGE","","52W","Options:Curr=USD,Mag=Standard,ConvMethod=R,FilingVer=Current/Restated")</f>
         <v>Price Change (%)</v>
       </c>
-      <c r="H5" s="36" t="s">
+      <c r="H5" s="6" t="s">
         <v>444</v>
       </c>
-      <c r="I5" s="36" t="str">
+      <c r="I5" s="6" t="str">
         <f>_xll.SNL.Clients.Office.Excel.Functions.SPGLabel(266637,"RD_CREDIT_RATING_DATE_GLOBAL","Issuer Credit Rating","Local Currency LT|Current","Options:Curr=USD,Mag=Standard,ConvMethod=R,FilingVer=Current/Restated")</f>
         <v>S&amp;P Credit Rating Date MM/dd/yyyy</v>
       </c>
@@ -8371,7 +8359,7 @@
         <v>Price Change (%)</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
         <v>18</v>
       </c>
@@ -8401,42 +8389,42 @@
         <v>58</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A7" s="37"/>
-      <c r="B7" s="38"/>
-      <c r="C7" s="38"/>
-      <c r="D7" s="38"/>
-      <c r="E7" s="38"/>
-      <c r="F7" s="38" t="str">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="13"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7" t="str">
         <f>_xll.SNL.Clients.Office.Excel.Functions.SPGLabel(266637,"RD_CREDIT_RATING_GLOBAL","&lt;&gt;Issuer Credit Rating")</f>
         <v>Issuer Credit Rating</v>
       </c>
-      <c r="G7" s="38"/>
-      <c r="H7" s="38"/>
-      <c r="I7" s="38" t="str">
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7" t="str">
         <f>_xll.SNL.Clients.Office.Excel.Functions.SPGLabel(266637,"RD_CREDIT_RATING_DATE_GLOBAL","&lt;&gt;Issuer Credit Rating")</f>
         <v>Issuer Credit Rating</v>
       </c>
       <c r="J7" s="7"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A8" s="37"/>
-      <c r="B8" s="38"/>
-      <c r="C8" s="38"/>
-      <c r="D8" s="38"/>
-      <c r="E8" s="38"/>
-      <c r="F8" s="38" t="str">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="13"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7" t="str">
         <f>_xll.SNL.Clients.Office.Excel.Functions.SPGLabel(266637,"RD_CREDIT_RATING_GLOBAL",,"&lt;&gt;Local Currency LT|Current")</f>
         <v>Local Currency LT|Current</v>
       </c>
-      <c r="G8" s="38" t="str">
+      <c r="G8" s="7" t="str">
         <f>_xll.SNL.Clients.Office.Excel.Functions.SPGLabel(266637,"SP_PRICE_CHANGE",,"&lt;&gt;52W")</f>
         <v>52W</v>
       </c>
-      <c r="H8" s="38" t="s">
+      <c r="H8" s="7" t="s">
         <v>443</v>
       </c>
-      <c r="I8" s="38" t="str">
+      <c r="I8" s="7" t="str">
         <f>_xll.SNL.Clients.Office.Excel.Functions.SPGLabel(266637,"RD_CREDIT_RATING_DATE_GLOBAL",,"&lt;&gt;Local Currency LT|Current")</f>
         <v>Local Currency LT|Current</v>
       </c>
@@ -8445,14 +8433,14 @@
         <v>1W</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
         <v>26</v>
       </c>
       <c r="B9" s="5">
         <v>4965910</v>
       </c>
-      <c r="C9" s="36" t="s">
+      <c r="C9" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D9" s="3">
@@ -8461,30 +8449,30 @@
       <c r="E9" s="3">
         <v>377.31</v>
       </c>
-      <c r="F9" s="36" t="s">
+      <c r="F9" s="6" t="s">
         <v>3</v>
       </c>
       <c r="G9" s="9">
         <v>736.62608899999998</v>
       </c>
-      <c r="H9" s="39">
+      <c r="H9" s="34">
         <v>1</v>
       </c>
-      <c r="I9" s="40">
+      <c r="I9" s="35">
         <v>45638</v>
       </c>
       <c r="J9" s="3">
         <v>7.6182569999999998</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
         <v>23</v>
       </c>
       <c r="B10" s="5">
         <v>6676338</v>
       </c>
-      <c r="C10" s="36" t="s">
+      <c r="C10" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D10" s="3">
@@ -8493,30 +8481,30 @@
       <c r="E10" s="3">
         <v>234.05</v>
       </c>
-      <c r="F10" s="36" t="s">
+      <c r="F10" s="6" t="s">
         <v>60</v>
       </c>
       <c r="G10" s="9">
         <v>456.86414500000001</v>
       </c>
-      <c r="H10" s="39">
+      <c r="H10" s="34">
         <v>1</v>
       </c>
-      <c r="I10" s="40">
+      <c r="I10" s="35">
         <v>45518</v>
       </c>
       <c r="J10" s="3">
         <v>23.845589</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
         <v>27</v>
       </c>
       <c r="B11" s="5">
         <v>4085953</v>
       </c>
-      <c r="C11" s="36" t="s">
+      <c r="C11" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D11" s="3">
@@ -8525,30 +8513,30 @@
       <c r="E11" s="9">
         <v>186.86</v>
       </c>
-      <c r="F11" s="36" t="s">
+      <c r="F11" s="6" t="s">
         <v>62</v>
       </c>
       <c r="G11" s="9">
         <v>376.31914399999999</v>
       </c>
-      <c r="H11" s="39">
+      <c r="H11" s="34">
         <v>1</v>
       </c>
-      <c r="I11" s="40">
+      <c r="I11" s="35">
         <v>45566</v>
       </c>
       <c r="J11" s="3">
         <v>-7.7283369999999998</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
         <v>24</v>
       </c>
       <c r="B12" s="5">
         <v>4057179</v>
       </c>
-      <c r="C12" s="36" t="s">
+      <c r="C12" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D12" s="3">
@@ -8557,30 +8545,30 @@
       <c r="E12" s="9">
         <v>5.75</v>
       </c>
-      <c r="F12" s="36" t="s">
+      <c r="F12" s="6" t="s">
         <v>61</v>
       </c>
       <c r="G12" s="9">
         <v>325.925926</v>
       </c>
-      <c r="H12" s="39">
+      <c r="H12" s="34">
         <v>1</v>
       </c>
-      <c r="I12" s="40">
+      <c r="I12" s="35">
         <v>45573</v>
       </c>
       <c r="J12" s="3">
         <v>13.907844000000001</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
         <v>31</v>
       </c>
       <c r="B13" s="5">
         <v>4915571</v>
       </c>
-      <c r="C13" s="36" t="s">
+      <c r="C13" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D13" s="3">
@@ -8589,30 +8577,30 @@
       <c r="E13" s="9">
         <v>152.61000000000001</v>
       </c>
-      <c r="F13" s="36" t="s">
+      <c r="F13" s="6" t="s">
         <v>64</v>
       </c>
       <c r="G13" s="9">
         <v>289.708887</v>
       </c>
-      <c r="H13" s="39">
+      <c r="H13" s="34">
         <v>1</v>
       </c>
-      <c r="I13" s="40">
+      <c r="I13" s="35">
         <v>44334</v>
       </c>
       <c r="J13" s="3">
         <v>7.7474610000000004</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
         <v>11</v>
       </c>
       <c r="B14" s="5">
         <v>4990350</v>
       </c>
-      <c r="C14" s="36" t="s">
+      <c r="C14" s="6" t="s">
         <v>22</v>
       </c>
       <c r="D14" s="3">
@@ -8621,30 +8609,30 @@
       <c r="E14" s="9">
         <v>316.26</v>
       </c>
-      <c r="F14" s="36" t="s">
+      <c r="F14" s="6" t="s">
         <v>3</v>
       </c>
       <c r="G14" s="9">
         <v>287.52603900000003</v>
       </c>
-      <c r="H14" s="39">
+      <c r="H14" s="34">
         <v>1</v>
       </c>
-      <c r="I14" s="40">
+      <c r="I14" s="35">
         <v>38775</v>
       </c>
       <c r="J14" s="3">
         <v>9.6377179999999996</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
         <v>29</v>
       </c>
       <c r="B15" s="5">
         <v>4945122</v>
       </c>
-      <c r="C15" s="36" t="s">
+      <c r="C15" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D15" s="3">
@@ -8653,30 +8641,30 @@
       <c r="E15" s="9">
         <v>75.995000000000005</v>
       </c>
-      <c r="F15" s="36" t="s">
+      <c r="F15" s="6" t="s">
         <v>3</v>
       </c>
       <c r="G15" s="9">
         <v>246.69251800000001</v>
       </c>
-      <c r="H15" s="39">
+      <c r="H15" s="34">
         <v>1</v>
       </c>
-      <c r="I15" s="40">
+      <c r="I15" s="35">
         <v>41605</v>
       </c>
       <c r="J15" s="3">
         <v>3.612676</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
         <v>36</v>
       </c>
       <c r="B16" s="5">
         <v>4004423</v>
       </c>
-      <c r="C16" s="36" t="s">
+      <c r="C16" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D16" s="3">
@@ -8685,30 +8673,30 @@
       <c r="E16" s="3">
         <v>207.3</v>
       </c>
-      <c r="F16" s="36" t="s">
+      <c r="F16" s="6" t="s">
         <v>65</v>
       </c>
       <c r="G16" s="9">
         <v>213.99575899999999</v>
       </c>
-      <c r="H16" s="39">
+      <c r="H16" s="34">
         <v>1</v>
       </c>
-      <c r="I16" s="40">
+      <c r="I16" s="35">
         <v>44972</v>
       </c>
       <c r="J16" s="3">
         <v>6.9561520000000003</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
         <v>30</v>
       </c>
       <c r="B17" s="5">
         <v>4096386</v>
       </c>
-      <c r="C17" s="36" t="s">
+      <c r="C17" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D17" s="3">
@@ -8717,30 +8705,30 @@
       <c r="E17" s="3">
         <v>146.25</v>
       </c>
-      <c r="F17" s="36" t="s">
+      <c r="F17" s="6" t="s">
         <v>3</v>
       </c>
       <c r="G17" s="9">
         <v>197.92218399999999</v>
       </c>
-      <c r="H17" s="39">
+      <c r="H17" s="34">
         <v>1</v>
       </c>
-      <c r="I17" s="40">
+      <c r="I17" s="35">
         <v>42143</v>
       </c>
       <c r="J17" s="3">
         <v>15.396825</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
         <v>35</v>
       </c>
       <c r="B18" s="5">
         <v>4144107</v>
       </c>
-      <c r="C18" s="36" t="s">
+      <c r="C18" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D18" s="3">
@@ -8749,30 +8737,30 @@
       <c r="E18" s="9">
         <v>34.35</v>
       </c>
-      <c r="F18" s="36" t="s">
+      <c r="F18" s="6" t="s">
         <v>63</v>
       </c>
       <c r="G18" s="9">
         <v>190.609137</v>
       </c>
-      <c r="H18" s="39">
+      <c r="H18" s="34">
         <v>1</v>
       </c>
-      <c r="I18" s="40">
+      <c r="I18" s="35">
         <v>45407</v>
       </c>
       <c r="J18" s="3">
         <v>-0.395619</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
         <v>44</v>
       </c>
       <c r="B19" s="5">
         <v>4994529</v>
       </c>
-      <c r="C19" s="36" t="s">
+      <c r="C19" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D19" s="3">
@@ -8781,30 +8769,30 @@
       <c r="E19" s="9">
         <v>107.97</v>
       </c>
-      <c r="F19" s="36" t="s">
+      <c r="F19" s="6" t="s">
         <v>65</v>
       </c>
       <c r="G19" s="9">
         <v>164.373164</v>
       </c>
-      <c r="H19" s="39">
+      <c r="H19" s="34">
         <v>1</v>
       </c>
-      <c r="I19" s="40">
+      <c r="I19" s="35">
         <v>45622</v>
       </c>
       <c r="J19" s="3">
         <v>10.755967</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
         <v>429</v>
       </c>
       <c r="B20" s="5">
         <v>11028051</v>
       </c>
-      <c r="C20" s="36" t="s">
+      <c r="C20" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D20" s="3">
@@ -8813,30 +8801,30 @@
       <c r="E20" s="3">
         <v>21.31</v>
       </c>
-      <c r="F20" s="36" t="s">
+      <c r="F20" s="6" t="s">
         <v>4</v>
       </c>
       <c r="G20" s="9">
         <v>159.24574200000001</v>
       </c>
-      <c r="H20" s="39">
+      <c r="H20" s="34">
         <v>1</v>
       </c>
-      <c r="I20" s="40">
+      <c r="I20" s="35">
         <v>45352</v>
       </c>
       <c r="J20" s="3">
         <v>-7.538303</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
         <v>34</v>
       </c>
       <c r="B21" s="5">
         <v>12805289</v>
       </c>
-      <c r="C21" s="36" t="s">
+      <c r="C21" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D21" s="3">
@@ -8845,30 +8833,30 @@
       <c r="E21" s="3">
         <v>295.85000000000002</v>
       </c>
-      <c r="F21" s="36" t="s">
+      <c r="F21" s="6" t="s">
         <v>64</v>
       </c>
       <c r="G21" s="9">
         <v>143.81902099999999</v>
       </c>
-      <c r="H21" s="39">
+      <c r="H21" s="34">
         <v>1</v>
       </c>
-      <c r="I21" s="40">
+      <c r="I21" s="35">
         <v>44937</v>
       </c>
       <c r="J21" s="3">
         <v>7.8195490000000003</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
         <v>430</v>
       </c>
       <c r="B22" s="5">
         <v>4303090</v>
       </c>
-      <c r="C22" s="36" t="s">
+      <c r="C22" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D22" s="3">
@@ -8877,30 +8865,30 @@
       <c r="E22" s="9">
         <v>44.38</v>
       </c>
-      <c r="F22" s="36" t="s">
+      <c r="F22" s="6" t="s">
         <v>64</v>
       </c>
       <c r="G22" s="9">
         <v>129.354005</v>
       </c>
-      <c r="H22" s="39">
+      <c r="H22" s="34">
         <v>1</v>
       </c>
-      <c r="I22" s="40">
+      <c r="I22" s="35">
         <v>45366</v>
       </c>
       <c r="J22" s="3">
         <v>8.8148149999999994</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
         <v>32</v>
       </c>
       <c r="B23" s="5">
         <v>4964205</v>
       </c>
-      <c r="C23" s="36" t="s">
+      <c r="C23" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D23" s="3">
@@ -8909,30 +8897,30 @@
       <c r="E23" s="3">
         <v>107.96</v>
       </c>
-      <c r="F23" s="36" t="s">
+      <c r="F23" s="6" t="s">
         <v>64</v>
       </c>
       <c r="G23" s="9">
         <v>124.916667</v>
       </c>
-      <c r="H23" s="39">
+      <c r="H23" s="34">
         <v>1</v>
       </c>
-      <c r="I23" s="40">
+      <c r="I23" s="35">
         <v>44014</v>
       </c>
       <c r="J23" s="3">
         <v>3.0912289999999998</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
         <v>8</v>
       </c>
       <c r="B24" s="5">
         <v>6858530</v>
       </c>
-      <c r="C24" s="36" t="s">
+      <c r="C24" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D24" s="3">
@@ -8941,30 +8929,30 @@
       <c r="E24" s="3">
         <v>92.78</v>
       </c>
-      <c r="F24" s="36" t="s">
+      <c r="F24" s="6" t="s">
         <v>63</v>
       </c>
       <c r="G24" s="9">
         <v>120.90476200000001</v>
       </c>
-      <c r="H24" s="39">
+      <c r="H24" s="34">
         <v>1</v>
       </c>
-      <c r="I24" s="40">
+      <c r="I24" s="35">
         <v>45586</v>
       </c>
       <c r="J24" s="3">
         <v>3.1538460000000001</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
         <v>431</v>
       </c>
       <c r="B25" s="5">
         <v>4038577</v>
       </c>
-      <c r="C25" s="36" t="s">
+      <c r="C25" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D25" s="3">
@@ -8973,30 +8961,30 @@
       <c r="E25" s="3">
         <v>65.069999999999993</v>
       </c>
-      <c r="F25" s="36" t="s">
+      <c r="F25" s="6" t="s">
         <v>64</v>
       </c>
       <c r="G25" s="9">
         <v>113.344262</v>
       </c>
-      <c r="H25" s="39">
+      <c r="H25" s="34">
         <v>1</v>
       </c>
-      <c r="I25" s="40">
+      <c r="I25" s="35">
         <v>45257</v>
       </c>
       <c r="J25" s="3">
         <v>4.1729320000000003</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
         <v>50</v>
       </c>
       <c r="B26" s="5">
         <v>4057436</v>
       </c>
-      <c r="C26" s="36" t="s">
+      <c r="C26" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D26" s="3">
@@ -9005,30 +8993,30 @@
       <c r="E26" s="3">
         <v>110.35</v>
       </c>
-      <c r="F26" s="36" t="s">
+      <c r="F26" s="6" t="s">
         <v>65</v>
       </c>
       <c r="G26" s="9">
         <v>112.089179</v>
       </c>
-      <c r="H26" s="39">
+      <c r="H26" s="34">
         <v>1</v>
       </c>
-      <c r="I26" s="40">
+      <c r="I26" s="35">
         <v>44986</v>
       </c>
       <c r="J26" s="3">
         <v>4.3198410000000003</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="14" t="s">
         <v>45</v>
       </c>
       <c r="B27" s="5">
         <v>4152750</v>
       </c>
-      <c r="C27" s="36" t="s">
+      <c r="C27" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D27" s="3">
@@ -9037,30 +9025,30 @@
       <c r="E27" s="3">
         <v>29.31</v>
       </c>
-      <c r="F27" s="36" t="s">
+      <c r="F27" s="6" t="s">
         <v>64</v>
       </c>
       <c r="G27" s="9">
         <v>110.409189</v>
       </c>
-      <c r="H27" s="39">
+      <c r="H27" s="34">
         <v>1</v>
       </c>
-      <c r="I27" s="40">
+      <c r="I27" s="35">
         <v>45316</v>
       </c>
       <c r="J27" s="3">
         <v>4.464188</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="14" t="s">
         <v>432</v>
       </c>
       <c r="B28" s="5">
         <v>4884349</v>
       </c>
-      <c r="C28" s="36" t="s">
+      <c r="C28" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D28" s="3">
@@ -9069,30 +9057,30 @@
       <c r="E28" s="3">
         <v>39.520000000000003</v>
       </c>
-      <c r="F28" s="36" t="s">
+      <c r="F28" s="6" t="s">
         <v>3</v>
       </c>
       <c r="G28" s="9">
         <v>108.658923</v>
       </c>
-      <c r="H28" s="39">
+      <c r="H28" s="34">
         <v>1</v>
       </c>
-      <c r="I28" s="40">
+      <c r="I28" s="35">
         <v>44664</v>
       </c>
       <c r="J28" s="3">
         <v>8.8777600000000003</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="14" t="s">
         <v>433</v>
       </c>
       <c r="B29" s="5">
         <v>28660777</v>
       </c>
-      <c r="C29" s="36" t="s">
+      <c r="C29" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D29" s="3">
@@ -9101,30 +9089,30 @@
       <c r="E29" s="3">
         <v>111.2</v>
       </c>
-      <c r="F29" s="36" t="s">
+      <c r="F29" s="6" t="s">
         <v>62</v>
       </c>
       <c r="G29" s="9">
         <v>105.773501</v>
       </c>
-      <c r="H29" s="39">
+      <c r="H29" s="34">
         <v>1</v>
       </c>
-      <c r="I29" s="40">
+      <c r="I29" s="35">
         <v>44333</v>
       </c>
       <c r="J29" s="3">
         <v>2.4811559999999999</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="14" t="s">
         <v>434</v>
       </c>
       <c r="B30" s="5">
         <v>4057224</v>
       </c>
-      <c r="C30" s="36" t="s">
+      <c r="C30" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D30" s="3">
@@ -9133,30 +9121,30 @@
       <c r="E30" s="3">
         <v>36.43</v>
       </c>
-      <c r="F30" s="36" t="s">
+      <c r="F30" s="6" t="s">
         <v>65</v>
       </c>
       <c r="G30" s="9">
         <v>102.27651299999999</v>
       </c>
-      <c r="H30" s="39">
+      <c r="H30" s="34">
         <v>1</v>
       </c>
-      <c r="I30" s="40">
+      <c r="I30" s="35">
         <v>41967</v>
       </c>
       <c r="J30" s="3">
         <v>8.0125250000000001</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="14" t="s">
         <v>435</v>
       </c>
       <c r="B31" s="5">
         <v>4225417</v>
       </c>
-      <c r="C31" s="36" t="s">
+      <c r="C31" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D31" s="3">
@@ -9165,30 +9153,30 @@
       <c r="E31" s="3">
         <v>34.950000000000003</v>
       </c>
-      <c r="F31" s="36" t="s">
+      <c r="F31" s="6" t="s">
         <v>3</v>
       </c>
       <c r="G31" s="9">
         <v>100.97757300000001</v>
       </c>
-      <c r="H31" s="39">
+      <c r="H31" s="34">
         <v>1</v>
       </c>
-      <c r="I31" s="40">
+      <c r="I31" s="35">
         <v>44642</v>
       </c>
       <c r="J31" s="3">
         <v>5.2749870000000003</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="14" t="s">
         <v>436</v>
       </c>
       <c r="B32" s="5">
         <v>11196767</v>
       </c>
-      <c r="C32" s="36" t="s">
+      <c r="C32" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D32" s="3">
@@ -9197,30 +9185,30 @@
       <c r="E32" s="3">
         <v>65.2</v>
       </c>
-      <c r="F32" s="36" t="s">
+      <c r="F32" s="6" t="s">
         <v>62</v>
       </c>
       <c r="G32" s="9">
         <v>100.615385</v>
       </c>
-      <c r="H32" s="39">
+      <c r="H32" s="34">
         <v>1</v>
       </c>
-      <c r="I32" s="40">
+      <c r="I32" s="35">
         <v>44713</v>
       </c>
       <c r="J32" s="3">
         <v>0.48266799999999999</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="14" t="s">
         <v>49</v>
       </c>
       <c r="B33" s="5">
         <v>4415853</v>
       </c>
-      <c r="C33" s="36" t="s">
+      <c r="C33" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D33" s="3">
@@ -9229,30 +9217,30 @@
       <c r="E33" s="3">
         <v>67.83</v>
       </c>
-      <c r="F33" s="36" t="s">
+      <c r="F33" s="6" t="s">
         <v>65</v>
       </c>
       <c r="G33" s="9">
         <v>98.333332999999996</v>
       </c>
-      <c r="H33" s="39">
+      <c r="H33" s="34">
         <v>1</v>
       </c>
-      <c r="I33" s="40">
+      <c r="I33" s="35">
         <v>45338</v>
       </c>
       <c r="J33" s="3">
         <v>12.946227</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="14" t="s">
         <v>55</v>
       </c>
       <c r="B34" s="5">
         <v>4263230</v>
       </c>
-      <c r="C34" s="36" t="s">
+      <c r="C34" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D34" s="3">
@@ -9261,30 +9249,30 @@
       <c r="E34" s="9">
         <v>27.65</v>
       </c>
-      <c r="F34" s="36" t="s">
+      <c r="F34" s="6" t="s">
         <v>3</v>
       </c>
       <c r="G34" s="9">
         <v>98.207885000000005</v>
       </c>
-      <c r="H34" s="39">
+      <c r="H34" s="34">
         <v>1</v>
       </c>
-      <c r="I34" s="40">
+      <c r="I34" s="35">
         <v>44806</v>
       </c>
       <c r="J34" s="3">
         <v>-3.8502559999999999</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="14" t="s">
         <v>437</v>
       </c>
       <c r="B35" s="5">
         <v>29619517</v>
       </c>
-      <c r="C35" s="36" t="s">
+      <c r="C35" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D35" s="3">
@@ -9293,30 +9281,30 @@
       <c r="E35" s="3">
         <v>20.420000000000002</v>
       </c>
-      <c r="F35" s="36" t="s">
+      <c r="F35" s="6" t="s">
         <v>64</v>
       </c>
       <c r="G35" s="9">
         <v>96.157540999999995</v>
       </c>
-      <c r="H35" s="39">
+      <c r="H35" s="34">
         <v>1</v>
       </c>
-      <c r="I35" s="40">
+      <c r="I35" s="35">
         <v>44893</v>
       </c>
       <c r="J35" s="3">
         <v>5.8493149999999998</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="14" t="s">
         <v>438</v>
       </c>
       <c r="B36" s="5">
         <v>6617441</v>
       </c>
-      <c r="C36" s="36" t="s">
+      <c r="C36" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D36" s="3">
@@ -9325,30 +9313,30 @@
       <c r="E36" s="3">
         <v>37.03</v>
       </c>
-      <c r="F36" s="36" t="s">
+      <c r="F36" s="6" t="s">
         <v>3</v>
       </c>
       <c r="G36" s="9">
         <v>91.765923999999998</v>
       </c>
-      <c r="H36" s="39">
+      <c r="H36" s="34">
         <v>1</v>
       </c>
-      <c r="I36" s="40">
+      <c r="I36" s="35">
         <v>40130</v>
       </c>
       <c r="J36" s="3">
         <v>5.081582</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="14" t="s">
         <v>39</v>
       </c>
       <c r="B37" s="5">
         <v>4205752</v>
       </c>
-      <c r="C37" s="36" t="s">
+      <c r="C37" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D37" s="3">
@@ -9357,30 +9345,30 @@
       <c r="E37" s="3">
         <v>63.7</v>
       </c>
-      <c r="F37" s="36" t="s">
+      <c r="F37" s="6" t="s">
         <v>3</v>
       </c>
       <c r="G37" s="9">
         <v>91.463780999999997</v>
       </c>
-      <c r="H37" s="39">
+      <c r="H37" s="34">
         <v>1</v>
       </c>
-      <c r="I37" s="40">
+      <c r="I37" s="35">
         <v>44127</v>
       </c>
       <c r="J37" s="3">
         <v>4.9266639999999997</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="14" t="s">
         <v>439</v>
       </c>
       <c r="B38" s="5">
         <v>4570533</v>
       </c>
-      <c r="C38" s="36" t="s">
+      <c r="C38" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="3">
@@ -9389,30 +9377,30 @@
       <c r="E38" s="3">
         <v>17.84</v>
       </c>
-      <c r="F38" s="36" t="s">
+      <c r="F38" s="6" t="s">
         <v>63</v>
       </c>
       <c r="G38" s="9">
         <v>91.211146999999997</v>
       </c>
-      <c r="H38" s="39">
+      <c r="H38" s="34">
         <v>1</v>
       </c>
-      <c r="I38" s="40">
+      <c r="I38" s="35">
         <v>45419</v>
       </c>
       <c r="J38" s="3">
         <v>0.35744100000000001</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="14" t="s">
         <v>41</v>
       </c>
       <c r="B39" s="5">
         <v>4980858</v>
       </c>
-      <c r="C39" s="36" t="s">
+      <c r="C39" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D39" s="3">
@@ -9421,30 +9409,30 @@
       <c r="E39" s="3">
         <v>236.16</v>
       </c>
-      <c r="F39" s="36" t="s">
+      <c r="F39" s="6" t="s">
         <v>62</v>
       </c>
       <c r="G39" s="9">
         <v>88.190293999999994</v>
       </c>
-      <c r="H39" s="39">
+      <c r="H39" s="34">
         <v>1</v>
       </c>
-      <c r="I39" s="40">
+      <c r="I39" s="35">
         <v>45330</v>
       </c>
       <c r="J39" s="3">
         <v>6.4066330000000002</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="14" t="s">
         <v>440</v>
       </c>
       <c r="B40" s="5">
         <v>4994468</v>
       </c>
-      <c r="C40" s="36" t="s">
+      <c r="C40" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D40" s="3">
@@ -9453,30 +9441,30 @@
       <c r="E40" s="3">
         <v>67.400000000000006</v>
       </c>
-      <c r="F40" s="36" t="s">
+      <c r="F40" s="6" t="s">
         <v>65</v>
       </c>
       <c r="G40" s="9">
         <v>88.163037000000003</v>
       </c>
-      <c r="H40" s="39">
+      <c r="H40" s="34">
         <v>1</v>
       </c>
-      <c r="I40" s="40">
+      <c r="I40" s="35">
         <v>44550</v>
       </c>
       <c r="J40" s="3">
         <v>8.1645570000000003</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="14" t="s">
         <v>441</v>
       </c>
       <c r="B41" s="5">
         <v>4121009</v>
       </c>
-      <c r="C41" s="36" t="s">
+      <c r="C41" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D41" s="3">
@@ -9485,30 +9473,30 @@
       <c r="E41" s="3">
         <v>29.75</v>
       </c>
-      <c r="F41" s="36" t="s">
+      <c r="F41" s="6" t="s">
         <v>64</v>
       </c>
       <c r="G41" s="9">
         <v>87.578815000000006</v>
       </c>
-      <c r="H41" s="39">
+      <c r="H41" s="34">
         <v>1</v>
       </c>
-      <c r="I41" s="40">
+      <c r="I41" s="35">
         <v>45351</v>
       </c>
       <c r="J41" s="3">
         <v>9.3799880000000009</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="14" t="s">
         <v>10</v>
       </c>
       <c r="B42" s="5">
         <v>4190757</v>
       </c>
-      <c r="C42" s="36" t="s">
+      <c r="C42" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D42" s="3">
@@ -9517,30 +9505,30 @@
       <c r="E42" s="3">
         <v>27.52</v>
       </c>
-      <c r="F42" s="36" t="s">
+      <c r="F42" s="6" t="s">
         <v>61</v>
       </c>
       <c r="G42" s="9">
         <v>86.956522000000007</v>
       </c>
-      <c r="H42" s="39">
+      <c r="H42" s="34">
         <v>1</v>
       </c>
-      <c r="I42" s="40">
+      <c r="I42" s="35">
         <v>45610</v>
       </c>
       <c r="J42" s="3">
         <v>3.5687169999999999</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="14" t="s">
         <v>442</v>
       </c>
       <c r="B43" s="5">
         <v>4810271</v>
       </c>
-      <c r="C43" s="36" t="s">
+      <c r="C43" s="6" t="s">
         <v>22</v>
       </c>
       <c r="D43" s="3">
@@ -9549,23 +9537,23 @@
       <c r="E43" s="3">
         <v>95.39</v>
       </c>
-      <c r="F43" s="36" t="s">
+      <c r="F43" s="6" t="s">
         <v>3</v>
       </c>
       <c r="G43" s="9">
         <v>86.782847000000004</v>
       </c>
-      <c r="H43" s="39">
+      <c r="H43" s="34">
         <v>1</v>
       </c>
-      <c r="I43" s="40">
+      <c r="I43" s="35">
         <v>44901</v>
       </c>
       <c r="J43" s="9">
         <v>7.9352429999999998</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="14" t="s">
         <v>107</v>
       </c>
@@ -9597,7 +9585,7 @@
         <v>-1.066856</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="14"/>
       <c r="B45" s="5"/>
       <c r="C45" s="6"/>
@@ -9607,7 +9595,7 @@
       <c r="H45" s="2"/>
       <c r="I45" s="8"/>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="14"/>
       <c r="B46" s="5"/>
       <c r="C46" s="6"/>
@@ -9617,7 +9605,7 @@
       <c r="H46" s="2"/>
       <c r="I46" s="8"/>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="14"/>
       <c r="B47" s="5"/>
       <c r="C47" s="6"/>
@@ -9627,7 +9615,7 @@
       <c r="H47" s="2"/>
       <c r="I47" s="8"/>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="14"/>
       <c r="B48" s="5"/>
       <c r="C48" s="6"/>
@@ -9637,7 +9625,7 @@
       <c r="H48" s="2"/>
       <c r="I48" s="8"/>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="14"/>
       <c r="B49" s="5"/>
       <c r="C49" s="6"/>
@@ -9647,7 +9635,7 @@
       <c r="H49" s="2"/>
       <c r="I49" s="8"/>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="14"/>
       <c r="B50" s="5"/>
       <c r="C50" s="6"/>
@@ -9657,7 +9645,7 @@
       <c r="H50" s="2"/>
       <c r="I50" s="8"/>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="14"/>
       <c r="B51" s="5"/>
       <c r="C51" s="6"/>
@@ -9667,7 +9655,7 @@
       <c r="H51" s="2"/>
       <c r="I51" s="8"/>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="14"/>
       <c r="B52" s="5"/>
       <c r="C52" s="6"/>
@@ -9677,7 +9665,7 @@
       <c r="H52" s="2"/>
       <c r="I52" s="8"/>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="14"/>
       <c r="B53" s="5"/>
       <c r="C53" s="6"/>
@@ -9687,7 +9675,7 @@
       <c r="H53" s="2"/>
       <c r="I53" s="8"/>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="14"/>
       <c r="B54" s="5"/>
       <c r="C54" s="6"/>
@@ -9697,7 +9685,7 @@
       <c r="H54" s="2"/>
       <c r="I54" s="8"/>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="14"/>
       <c r="B55" s="5"/>
       <c r="C55" s="6"/>
@@ -9707,7 +9695,7 @@
       <c r="H55" s="2"/>
       <c r="I55" s="8"/>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="14"/>
       <c r="B56" s="5"/>
       <c r="C56" s="6"/>
@@ -9717,7 +9705,7 @@
       <c r="H56" s="2"/>
       <c r="I56" s="8"/>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="14"/>
       <c r="B57" s="5"/>
       <c r="C57" s="6"/>
@@ -9727,7 +9715,7 @@
       <c r="H57" s="2"/>
       <c r="I57" s="8"/>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="14"/>
       <c r="B58" s="5"/>
       <c r="C58" s="6"/>
@@ -9737,7 +9725,7 @@
       <c r="H58" s="2"/>
       <c r="I58" s="8"/>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="14"/>
       <c r="B59" s="5"/>
       <c r="C59" s="6"/>
@@ -9747,7 +9735,7 @@
       <c r="H59" s="2"/>
       <c r="I59" s="8"/>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="14"/>
       <c r="B60" s="5"/>
       <c r="C60" s="6"/>
@@ -9757,7 +9745,7 @@
       <c r="H60" s="2"/>
       <c r="I60" s="8"/>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="14"/>
       <c r="B61" s="5"/>
       <c r="C61" s="6"/>
@@ -9767,7 +9755,7 @@
       <c r="H61" s="2"/>
       <c r="I61" s="8"/>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="14"/>
       <c r="B62" s="5"/>
       <c r="C62" s="6"/>
@@ -9777,7 +9765,7 @@
       <c r="H62" s="2"/>
       <c r="I62" s="8"/>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="14"/>
       <c r="B63" s="5"/>
       <c r="C63" s="6"/>
@@ -9787,7 +9775,7 @@
       <c r="H63" s="2"/>
       <c r="I63" s="8"/>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="14"/>
       <c r="B64" s="5"/>
       <c r="C64" s="6"/>
@@ -9797,7 +9785,7 @@
       <c r="H64" s="2"/>
       <c r="I64" s="8"/>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" s="14"/>
       <c r="B65" s="5"/>
       <c r="C65" s="6"/>
@@ -9807,7 +9795,7 @@
       <c r="H65" s="2"/>
       <c r="I65" s="8"/>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="14"/>
       <c r="B66" s="5"/>
       <c r="C66" s="6"/>
@@ -9817,7 +9805,7 @@
       <c r="H66" s="2"/>
       <c r="I66" s="8"/>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="14"/>
       <c r="B67" s="5"/>
       <c r="C67" s="6"/>
@@ -9827,7 +9815,7 @@
       <c r="H67" s="2"/>
       <c r="I67" s="8"/>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="14"/>
       <c r="B68" s="5"/>
       <c r="C68" s="6"/>
@@ -9837,7 +9825,7 @@
       <c r="H68" s="2"/>
       <c r="I68" s="8"/>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" s="14"/>
       <c r="B69" s="5"/>
       <c r="C69" s="6"/>
@@ -9847,7 +9835,7 @@
       <c r="H69" s="2"/>
       <c r="I69" s="8"/>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" s="14"/>
       <c r="B70" s="5"/>
       <c r="C70" s="6"/>
@@ -9857,7 +9845,7 @@
       <c r="H70" s="2"/>
       <c r="I70" s="8"/>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="14"/>
       <c r="B71" s="5"/>
       <c r="C71" s="6"/>
@@ -9867,7 +9855,7 @@
       <c r="H71" s="2"/>
       <c r="I71" s="8"/>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" s="14"/>
       <c r="B72" s="5"/>
       <c r="C72" s="6"/>
@@ -9877,7 +9865,7 @@
       <c r="H72" s="2"/>
       <c r="I72" s="8"/>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" s="14"/>
       <c r="B73" s="5"/>
       <c r="C73" s="6"/>
@@ -9887,7 +9875,7 @@
       <c r="H73" s="2"/>
       <c r="I73" s="8"/>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" s="14"/>
       <c r="B74" s="5"/>
       <c r="C74" s="6"/>
@@ -9897,7 +9885,7 @@
       <c r="H74" s="2"/>
       <c r="I74" s="8"/>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" s="14"/>
       <c r="B75" s="5"/>
       <c r="C75" s="6"/>
@@ -9907,7 +9895,7 @@
       <c r="H75" s="2"/>
       <c r="I75" s="8"/>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" s="14"/>
       <c r="B76" s="5"/>
       <c r="C76" s="6"/>
@@ -9917,7 +9905,7 @@
       <c r="H76" s="2"/>
       <c r="I76" s="8"/>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" s="14"/>
       <c r="B77" s="5"/>
       <c r="C77" s="6"/>
@@ -9927,7 +9915,7 @@
       <c r="H77" s="2"/>
       <c r="I77" s="8"/>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" s="14"/>
       <c r="B78" s="5"/>
       <c r="C78" s="6"/>
@@ -9937,7 +9925,7 @@
       <c r="H78" s="2"/>
       <c r="I78" s="8"/>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" s="14"/>
       <c r="B79" s="5"/>
       <c r="C79" s="6"/>
@@ -9947,7 +9935,7 @@
       <c r="H79" s="2"/>
       <c r="I79" s="8"/>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" s="14"/>
       <c r="B80" s="5"/>
       <c r="C80" s="6"/>
@@ -9957,7 +9945,7 @@
       <c r="H80" s="2"/>
       <c r="I80" s="8"/>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="14"/>
       <c r="B81" s="5"/>
       <c r="C81" s="6"/>
@@ -9967,7 +9955,7 @@
       <c r="H81" s="2"/>
       <c r="I81" s="8"/>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" s="14"/>
       <c r="B82" s="5"/>
       <c r="C82" s="6"/>
@@ -9977,7 +9965,7 @@
       <c r="H82" s="2"/>
       <c r="I82" s="8"/>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" s="14"/>
       <c r="B83" s="5"/>
       <c r="C83" s="6"/>
@@ -9987,7 +9975,7 @@
       <c r="H83" s="2"/>
       <c r="I83" s="8"/>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" s="14"/>
       <c r="B84" s="5"/>
       <c r="C84" s="6"/>
@@ -9997,7 +9985,7 @@
       <c r="H84" s="2"/>
       <c r="I84" s="8"/>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" s="14"/>
       <c r="B85" s="5"/>
       <c r="C85" s="6"/>
@@ -10007,7 +9995,7 @@
       <c r="H85" s="2"/>
       <c r="I85" s="8"/>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" s="14"/>
       <c r="B86" s="5"/>
       <c r="C86" s="6"/>
@@ -10017,7 +10005,7 @@
       <c r="H86" s="2"/>
       <c r="I86" s="8"/>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" s="14"/>
       <c r="B87" s="5"/>
       <c r="C87" s="6"/>
@@ -10027,7 +10015,7 @@
       <c r="H87" s="2"/>
       <c r="I87" s="8"/>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" s="14"/>
       <c r="B88" s="5"/>
       <c r="C88" s="6"/>
@@ -10048,36 +10036,36 @@
     <tabColor theme="9"/>
   </sheetPr>
   <dimension ref="A1:J94"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25" outlineLevelCol="1" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="47.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.53125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="3" max="3" width="12.86328125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="4" max="4" width="12.86328125" style="1" customWidth="1" collapsed="1"/>
+    <col min="1" max="1" width="47.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5703125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="3" max="3" width="12.85546875" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="4" max="4" width="12.85546875" style="1" customWidth="1" collapsed="1"/>
     <col min="5" max="5" width="23" style="1" customWidth="1"/>
     <col min="6" max="6" width="42" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="7" max="7" width="24.86328125" style="1" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="81.46484375" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="9" max="9" width="16.796875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="39.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="8.86328125" style="1"/>
+    <col min="7" max="7" width="24.85546875" style="1" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="81.42578125" style="1" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="9" max="9" width="16.85546875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="39.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.45"/>
-    <row r="2" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="3" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.45"/>
-    <row r="4" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.45"/>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="str">
         <f>_xll.SNL.Clients.Office.Excel.Functions.SPGTable($B$10:$B$94,$C$7:$J$7,,"Options:Curr=USD,Mag=Standard,ConvMethod=R,FilingVer=Current/Restated")</f>
         <v>SPGTable</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="str">
         <f>_xll.SNL.Clients.Office.Excel.Functions.SPGLabel(266637,"SP_ENTITY_NAME","","","Options:Curr=USD,Mag=Standard,ConvMethod=R,FilingVer=Current/Restated")</f>
         <v>Entity Name</v>
@@ -10119,7 +10107,7 @@
         <v>Average Weekly Volume/ Shares Out (%)</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
         <v>18</v>
       </c>
@@ -10151,7 +10139,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="13"/>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
@@ -10166,7 +10154,7 @@
       <c r="I8" s="7"/>
       <c r="J8" s="7"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="13"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
@@ -10184,7 +10172,7 @@
         <v>52W</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
         <v>103</v>
       </c>
@@ -10216,7 +10204,7 @@
         <v>81.284304770340881</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
         <v>82</v>
       </c>
@@ -10248,7 +10236,7 @@
         <v>53.715780687016668</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
         <v>26</v>
       </c>
@@ -10280,7 +10268,7 @@
         <v>41.816100577562061</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
         <v>129</v>
       </c>
@@ -10312,7 +10300,7 @@
         <v>35.986898127117207</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
         <v>34</v>
       </c>
@@ -10344,7 +10332,7 @@
         <v>25.949297537372583</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
         <v>136</v>
       </c>
@@ -10376,7 +10364,7 @@
         <v>24.172552350374875</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
         <v>73</v>
       </c>
@@ -10408,7 +10396,7 @@
         <v>25.629803358068965</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
         <v>114</v>
       </c>
@@ -10440,7 +10428,7 @@
         <v>22.322183666572638</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
         <v>23</v>
       </c>
@@ -10472,7 +10460,7 @@
         <v>17.303310385989992</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
         <v>55</v>
       </c>
@@ -10504,7 +10492,7 @@
         <v>21.376623911218157</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
         <v>68</v>
       </c>
@@ -10536,7 +10524,7 @@
         <v>15.506551637628624</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
         <v>194</v>
       </c>
@@ -10568,7 +10556,7 @@
         <v>20.218643006219583</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
         <v>95</v>
       </c>
@@ -10600,7 +10588,7 @@
         <v>24.977576441854001</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
         <v>99</v>
       </c>
@@ -10632,7 +10620,7 @@
         <v>29.806600469530693</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
         <v>48</v>
       </c>
@@ -10664,7 +10652,7 @@
         <v>17.533527066621357</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
         <v>85</v>
       </c>
@@ -10690,7 +10678,7 @@
         <v>16.199034263636118</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
         <v>31</v>
       </c>
@@ -10722,7 +10710,7 @@
         <v>15.725320753724068</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="14" t="s">
         <v>13</v>
       </c>
@@ -10754,7 +10742,7 @@
         <v>16.822395472602356</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="14" t="s">
         <v>126</v>
       </c>
@@ -10786,7 +10774,7 @@
         <v>11.483988666168301</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="14" t="s">
         <v>110</v>
       </c>
@@ -10818,7 +10806,7 @@
         <v>14.514139206656592</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="14" t="s">
         <v>123</v>
       </c>
@@ -10850,7 +10838,7 @@
         <v>14.047341093078366</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="14" t="s">
         <v>44</v>
       </c>
@@ -10882,7 +10870,7 @@
         <v>11.769556875404978</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="14" t="s">
         <v>29</v>
       </c>
@@ -10914,7 +10902,7 @@
         <v>10.952231935672883</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="14" t="s">
         <v>45</v>
       </c>
@@ -10946,7 +10934,7 @@
         <v>11.450502283111112</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="14" t="s">
         <v>80</v>
       </c>
@@ -10978,7 +10966,7 @@
         <v>12.252519010476846</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="14" t="s">
         <v>120</v>
       </c>
@@ -11010,7 +10998,7 @@
         <v>11.858070119393595</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="14" t="s">
         <v>132</v>
       </c>
@@ -11042,7 +11030,7 @@
         <v>10.79812130567004</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="14" t="s">
         <v>117</v>
       </c>
@@ -11074,7 +11062,7 @@
         <v>11.574683266333082</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="14" t="s">
         <v>52</v>
       </c>
@@ -11106,7 +11094,7 @@
         <v>11.15456518195051</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="14" t="s">
         <v>14</v>
       </c>
@@ -11138,7 +11126,7 @@
         <v>13.217403015215373</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="14" t="s">
         <v>195</v>
       </c>
@@ -11170,7 +11158,7 @@
         <v>10.122884822827928</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="14" t="s">
         <v>75</v>
       </c>
@@ -11202,7 +11190,7 @@
         <v>10.397235666536412</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="14" t="s">
         <v>35</v>
       </c>
@@ -11234,7 +11222,7 @@
         <v>10.173720789815476</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="14" t="s">
         <v>27</v>
       </c>
@@ -11266,7 +11254,7 @@
         <v>10.225083381948291</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="14" t="s">
         <v>24</v>
       </c>
@@ -11298,7 +11286,7 @@
         <v>9.3228249041054649</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="14" t="s">
         <v>98</v>
       </c>
@@ -11330,7 +11318,7 @@
         <v>8.8552402735918871</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="14" t="s">
         <v>71</v>
       </c>
@@ -11362,7 +11350,7 @@
         <v>5.2803521616799731</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="14" t="s">
         <v>109</v>
       </c>
@@ -11394,7 +11382,7 @@
         <v>7.9950900588338953</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="14" t="s">
         <v>91</v>
       </c>
@@ -11426,7 +11414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="14" t="s">
         <v>108</v>
       </c>
@@ -11458,7 +11446,7 @@
         <v>7.4272183959983664</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="14" t="s">
         <v>96</v>
       </c>
@@ -11490,7 +11478,7 @@
         <v>8.753778179102147</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="14" t="s">
         <v>37</v>
       </c>
@@ -11522,7 +11510,7 @@
         <v>6.7246616273116437</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="14" t="s">
         <v>127</v>
       </c>
@@ -11554,7 +11542,7 @@
         <v>7.4918960721868366</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="14" t="s">
         <v>105</v>
       </c>
@@ -11586,7 +11574,7 @@
         <v>7.8566953487283788</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" s="14" t="s">
         <v>54</v>
       </c>
@@ -11618,7 +11606,7 @@
         <v>7.0140434399395266</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" s="14" t="s">
         <v>118</v>
       </c>
@@ -11650,7 +11638,7 @@
         <v>6.6377137902392453</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="14" t="s">
         <v>32</v>
       </c>
@@ -11682,7 +11670,7 @@
         <v>7.7471534904616641</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="14" t="s">
         <v>67</v>
       </c>
@@ -11714,7 +11702,7 @@
         <v>7.4003127954687704</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" s="14" t="s">
         <v>51</v>
       </c>
@@ -11746,7 +11734,7 @@
         <v>6.3936260708298054</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" s="14" t="s">
         <v>133</v>
       </c>
@@ -11778,7 +11766,7 @@
         <v>7.0081721435898876</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" s="14" t="s">
         <v>196</v>
       </c>
@@ -11810,7 +11798,7 @@
         <v>6.48682372026565</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" s="14" t="s">
         <v>25</v>
       </c>
@@ -11842,7 +11830,7 @@
         <v>7.8133059310242157</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" s="14" t="s">
         <v>86</v>
       </c>
@@ -11874,7 +11862,7 @@
         <v>7.7756713428267688</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" s="14" t="s">
         <v>87</v>
       </c>
@@ -11906,7 +11894,7 @@
         <v>6.8137831938256896</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" s="14" t="s">
         <v>197</v>
       </c>
@@ -11938,7 +11926,7 @@
         <v>6.8424355029123447</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" s="14" t="s">
         <v>30</v>
       </c>
@@ -11970,7 +11958,7 @@
         <v>6.7169194550077531</v>
       </c>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" s="14" t="s">
         <v>38</v>
       </c>
@@ -12002,7 +11990,7 @@
         <v>6.1639397159961913</v>
       </c>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" s="14" t="s">
         <v>33</v>
       </c>
@@ -12034,7 +12022,7 @@
         <v>6.5473879933120926</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" s="14" t="s">
         <v>135</v>
       </c>
@@ -12066,7 +12054,7 @@
         <v>9.5897645171699111</v>
       </c>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" s="14" t="s">
         <v>10</v>
       </c>
@@ -12098,7 +12086,7 @@
         <v>5.024399377612947</v>
       </c>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" s="14" t="s">
         <v>46</v>
       </c>
@@ -12130,7 +12118,7 @@
         <v>5.411828867952746</v>
       </c>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" s="14" t="s">
         <v>134</v>
       </c>
@@ -12162,7 +12150,7 @@
         <v>5.7983801710200877</v>
       </c>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" s="14" t="s">
         <v>97</v>
       </c>
@@ -12194,7 +12182,7 @@
         <v>6.1374924867688279</v>
       </c>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" s="14" t="s">
         <v>89</v>
       </c>
@@ -12226,7 +12214,7 @@
         <v>5.8039815538645447</v>
       </c>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" s="14" t="s">
         <v>69</v>
       </c>
@@ -12258,7 +12246,7 @@
         <v>6.3593038038884497</v>
       </c>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" s="14" t="s">
         <v>198</v>
       </c>
@@ -12290,7 +12278,7 @@
         <v>6.1381962456839556</v>
       </c>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" s="14" t="s">
         <v>36</v>
       </c>
@@ -12322,7 +12310,7 @@
         <v>6.4832723166750723</v>
       </c>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" s="14" t="s">
         <v>94</v>
       </c>
@@ -12354,7 +12342,7 @@
         <v>6.2639505527828838</v>
       </c>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" s="14" t="s">
         <v>199</v>
       </c>
@@ -12386,7 +12374,7 @@
         <v>5.5620598180106926</v>
       </c>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" s="14" t="s">
         <v>124</v>
       </c>
@@ -12418,7 +12406,7 @@
         <v>7.8469675433418669</v>
       </c>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" s="14" t="s">
         <v>131</v>
       </c>
@@ -12450,7 +12438,7 @@
         <v>6.1704647277016766</v>
       </c>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" s="14" t="s">
         <v>12</v>
       </c>
@@ -12482,7 +12470,7 @@
         <v>5.3462583863771309</v>
       </c>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" s="14" t="s">
         <v>16</v>
       </c>
@@ -12514,7 +12502,7 @@
         <v>5.7062225392059842</v>
       </c>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83" s="14" t="s">
         <v>7</v>
       </c>
@@ -12546,7 +12534,7 @@
         <v>5.3861826012601401</v>
       </c>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" s="14" t="s">
         <v>113</v>
       </c>
@@ -12578,7 +12566,7 @@
         <v>5.1992654328044496</v>
       </c>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" s="14" t="s">
         <v>111</v>
       </c>
@@ -12610,7 +12598,7 @@
         <v>6.2696719156535474</v>
       </c>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86" s="14" t="s">
         <v>92</v>
       </c>
@@ -12642,7 +12630,7 @@
         <v>4.8957393842712467</v>
       </c>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87" s="14" t="s">
         <v>130</v>
       </c>
@@ -12674,7 +12662,7 @@
         <v>6.0340326797233867</v>
       </c>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A88" s="14" t="s">
         <v>77</v>
       </c>
@@ -12706,7 +12694,7 @@
         <v>4.8556049650992277</v>
       </c>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A89" s="14" t="s">
         <v>84</v>
       </c>
@@ -12738,7 +12726,7 @@
         <v>4.9292302046810974</v>
       </c>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A90" s="14" t="s">
         <v>106</v>
       </c>
@@ -12770,7 +12758,7 @@
         <v>5.2827629130296616</v>
       </c>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91" s="14" t="s">
         <v>200</v>
       </c>
@@ -12802,7 +12790,7 @@
         <v>5.9329526434653479</v>
       </c>
     </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92" s="14" t="s">
         <v>93</v>
       </c>
@@ -12834,7 +12822,7 @@
         <v>5.0380701894158113</v>
       </c>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A93" s="14" t="s">
         <v>101</v>
       </c>
@@ -12866,7 +12854,7 @@
         <v>5.006364280225081</v>
       </c>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A94" s="14" t="s">
         <v>47</v>
       </c>
@@ -12909,27 +12897,29 @@
     <tabColor theme="9"/>
   </sheetPr>
   <dimension ref="A1:U53"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25" outlineLevelCol="1" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" outlineLevelCol="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="47.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="8.86328125" style="1" customWidth="1" outlineLevel="1"/>
-    <col min="4" max="16384" width="8.86328125" style="1"/>
+    <col min="1" max="1" width="47.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="8.85546875" style="1" customWidth="1" outlineLevel="1"/>
+    <col min="4" max="5" width="8.85546875" style="1"/>
+    <col min="6" max="6" width="20.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.45"/>
-    <row r="2" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="3" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.45"/>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:21" s="4" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" t="str">
         <f>_xll.SNL.Clients.Office.Excel.Functions.SPGTable($B$9:$B$53,$C$6:$U$6,,"Options:Curr=USD,Mag=Standard,ConvMethod=R,FilingVer=Current/Restated")</f>
         <v>SPGTable</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="str">
         <f>_xll.SNL.Clients.Office.Excel.Functions.SPGLabel(266637,"SP_ENTITY_NAME","","","Options:Curr=USD,Mag=Standard,ConvMethod=R,FilingVer=Current/Restated")</f>
         <v>Entity Name</v>
@@ -13015,7 +13005,7 @@
         <v>Price Change (%)</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
         <v>18</v>
       </c>
@@ -13080,7 +13070,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7" s="13"/>
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
@@ -13112,7 +13102,7 @@
       </c>
       <c r="U7" s="7"/>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8" s="13"/>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
@@ -13150,7 +13140,7 @@
         <v>52W</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
         <v>119</v>
       </c>
@@ -13211,7 +13201,7 @@
         <v>633.962264</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
         <v>277</v>
       </c>
@@ -13270,7 +13260,7 @@
         <v>1399.5</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
         <v>278</v>
       </c>
@@ -13329,7 +13319,7 @@
         <v>246.996466</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
         <v>199</v>
       </c>
@@ -13390,7 +13380,7 @@
         <v>196.06299200000001</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
         <v>279</v>
       </c>
@@ -13451,7 +13441,7 @@
         <v>821.45289400000001</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
         <v>25</v>
       </c>
@@ -13516,7 +13506,7 @@
         <v>735.18817799999999</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
         <v>280</v>
       </c>
@@ -13575,7 +13565,7 @@
         <v>328.81536799999998</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
         <v>281</v>
       </c>
@@ -13636,7 +13626,7 @@
         <v>114.009142</v>
       </c>
     </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
         <v>202</v>
       </c>
@@ -13695,7 +13685,7 @@
         <v>77.154047000000006</v>
       </c>
     </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
         <v>282</v>
       </c>
@@ -13754,7 +13744,7 @@
         <v>200.657895</v>
       </c>
     </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
         <v>283</v>
       </c>
@@ -13813,7 +13803,7 @@
         <v>163.63636399999999</v>
       </c>
     </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
         <v>284</v>
       </c>
@@ -13872,7 +13862,7 @@
         <v>602.312139</v>
       </c>
     </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
         <v>80</v>
       </c>
@@ -13931,7 +13921,7 @@
         <v>157.92224100000001</v>
       </c>
     </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
         <v>285</v>
       </c>
@@ -13992,7 +13982,7 @@
         <v>153.28185300000001</v>
       </c>
     </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
         <v>286</v>
       </c>
@@ -14051,7 +14041,7 @@
         <v>-76.811807999999999</v>
       </c>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
         <v>287</v>
       </c>
@@ -14110,7 +14100,7 @@
         <v>110.175439</v>
       </c>
     </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
         <v>117</v>
       </c>
@@ -14169,7 +14159,7 @@
         <v>364.01480099999998</v>
       </c>
     </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
         <v>197</v>
       </c>
@@ -14228,7 +14218,7 @@
         <v>98.413630999999995</v>
       </c>
     </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="14" t="s">
         <v>123</v>
       </c>
@@ -14287,7 +14277,7 @@
         <v>184.195122</v>
       </c>
     </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="14" t="s">
         <v>100</v>
       </c>
@@ -14346,7 +14336,7 @@
         <v>191.5</v>
       </c>
     </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="14" t="s">
         <v>136</v>
       </c>
@@ -14405,7 +14395,7 @@
         <v>17.496444</v>
       </c>
     </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="14" t="s">
         <v>196</v>
       </c>
@@ -14464,7 +14454,7 @@
         <v>-16.804245000000002</v>
       </c>
     </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="14" t="s">
         <v>288</v>
       </c>
@@ -14519,7 +14509,7 @@
         <v>245.831534</v>
       </c>
     </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="14" t="s">
         <v>289</v>
       </c>
@@ -14580,7 +14570,7 @@
         <v>110.062893</v>
       </c>
     </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="14" t="s">
         <v>290</v>
       </c>
@@ -14639,7 +14629,7 @@
         <v>105.46218500000001</v>
       </c>
     </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="14" t="s">
         <v>200</v>
       </c>
@@ -14698,7 +14688,7 @@
         <v>11.518625</v>
       </c>
     </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="14" t="s">
         <v>291</v>
       </c>
@@ -14757,7 +14747,7 @@
         <v>229.452055</v>
       </c>
     </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="14" t="s">
         <v>292</v>
       </c>
@@ -14818,7 +14808,7 @@
         <v>133.02540400000001</v>
       </c>
     </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="14" t="s">
         <v>190</v>
       </c>
@@ -14881,7 +14871,7 @@
         <v>254.42260400000001</v>
       </c>
     </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="14" t="s">
         <v>191</v>
       </c>
@@ -14940,7 +14930,7 @@
         <v>134.52768699999999</v>
       </c>
     </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="14" t="s">
         <v>198</v>
       </c>
@@ -15001,7 +14991,7 @@
         <v>50.904279000000002</v>
       </c>
     </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="14" t="s">
         <v>127</v>
       </c>
@@ -15062,7 +15052,7 @@
         <v>138.06016</v>
       </c>
     </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="14" t="s">
         <v>293</v>
       </c>
@@ -15121,7 +15111,7 @@
         <v>-84.714674000000002</v>
       </c>
     </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="14" t="s">
         <v>115</v>
       </c>
@@ -15182,7 +15172,7 @@
         <v>48.368383000000001</v>
       </c>
     </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="14" t="s">
         <v>83</v>
       </c>
@@ -15241,7 +15231,7 @@
         <v>104.45103899999999</v>
       </c>
     </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="14" t="s">
         <v>203</v>
       </c>
@@ -15300,7 +15290,7 @@
         <v>46.904128</v>
       </c>
     </row>
-    <row r="45" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="14" t="s">
         <v>86</v>
       </c>
@@ -15359,7 +15349,7 @@
         <v>293.10344800000001</v>
       </c>
     </row>
-    <row r="46" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="14" t="s">
         <v>114</v>
       </c>
@@ -15416,7 +15406,7 @@
         <v>264.274385</v>
       </c>
     </row>
-    <row r="47" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="14" t="s">
         <v>129</v>
       </c>
@@ -15477,7 +15467,7 @@
         <v>94.683695</v>
       </c>
     </row>
-    <row r="48" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="14" t="s">
         <v>294</v>
       </c>
@@ -15538,7 +15528,7 @@
         <v>-6.5315320000000003</v>
       </c>
     </row>
-    <row r="49" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="14" t="s">
         <v>295</v>
       </c>
@@ -15597,7 +15587,7 @@
         <v>82.027998999999994</v>
       </c>
     </row>
-    <row r="50" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="14" t="s">
         <v>296</v>
       </c>
@@ -15656,7 +15646,7 @@
         <v>-34.773446</v>
       </c>
     </row>
-    <row r="51" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="14" t="s">
         <v>81</v>
       </c>
@@ -15715,7 +15705,7 @@
         <v>108.5</v>
       </c>
     </row>
-    <row r="52" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="14" t="s">
         <v>72</v>
       </c>
@@ -15772,7 +15762,7 @@
         <v>137.562715</v>
       </c>
     </row>
-    <row r="53" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="14" t="s">
         <v>39</v>
       </c>
@@ -15844,26 +15834,26 @@
     <tabColor theme="9"/>
   </sheetPr>
   <dimension ref="A1:H47"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.06640625" customWidth="1"/>
-    <col min="2" max="16384" width="8.86328125" style="22"/>
+    <col min="1" max="1" width="9" customWidth="1"/>
+    <col min="2" max="16384" width="8.85546875" style="22"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.45"/>
-    <row r="2" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="3" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.45"/>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="str">
         <f>_xll.SNL.Clients.Office.Excel.Functions.SPGTable($B$9:$B$47,$C$6:$H$6,,"Options:Curr=USD,Mag=Standard,ConvMethod=R,FilingVer=Current/Restated")</f>
         <v>SPGTable</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="str">
         <f>_xll.SNL.Clients.Office.Excel.Functions.SPGLabel(266637,"SP_ENTITY_NAME","","","Options:Curr=USD,Mag=Standard,ConvMethod=R,FilingVer=Current/Restated")</f>
         <v>Entity Name</v>
@@ -15897,7 +15887,7 @@
         <v>Avg Daily Volume/ One Year Avg Daily Volume (%)</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
         <v>18</v>
       </c>
@@ -15923,7 +15913,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="13"/>
       <c r="B7" s="25" t="s">
         <v>410</v>
@@ -15935,7 +15925,7 @@
       <c r="G7" s="25"/>
       <c r="H7" s="25"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="13"/>
       <c r="B8" s="25"/>
       <c r="C8" s="25"/>
@@ -15954,7 +15944,7 @@
         <v>1M</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
         <v>103</v>
       </c>
@@ -15980,7 +15970,7 @@
         <v>72.58</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
         <v>82</v>
       </c>
@@ -16006,7 +15996,7 @@
         <v>74.78</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
         <v>26</v>
       </c>
@@ -16032,7 +16022,7 @@
         <v>110.22</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
         <v>99</v>
       </c>
@@ -16058,7 +16048,7 @@
         <v>304.77</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
         <v>129</v>
       </c>
@@ -16084,7 +16074,7 @@
         <v>65.83</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
         <v>116</v>
       </c>
@@ -16110,7 +16100,7 @@
         <v>108.89</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
         <v>34</v>
       </c>
@@ -16136,7 +16126,7 @@
         <v>70.739999999999995</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
         <v>104</v>
       </c>
@@ -16162,7 +16152,7 @@
         <v>144.62</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
         <v>112</v>
       </c>
@@ -16188,7 +16178,7 @@
         <v>69.52</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
         <v>114</v>
       </c>
@@ -16214,7 +16204,7 @@
         <v>88.42</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="14" t="s">
         <v>121</v>
       </c>
@@ -16240,7 +16230,7 @@
         <v>83.55</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
         <v>70</v>
       </c>
@@ -16266,7 +16256,7 @@
         <v>78.14</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="14" t="s">
         <v>122</v>
       </c>
@@ -16292,7 +16282,7 @@
         <v>88.28</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
         <v>136</v>
       </c>
@@ -16318,7 +16308,7 @@
         <v>92.46</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="14" t="s">
         <v>85</v>
       </c>
@@ -16344,7 +16334,7 @@
         <v>92.64</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
         <v>14</v>
       </c>
@@ -16370,7 +16360,7 @@
         <v>147.07</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
         <v>102</v>
       </c>
@@ -16396,7 +16386,7 @@
         <v>91.59</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
         <v>35</v>
       </c>
@@ -16422,7 +16412,7 @@
         <v>106.28</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="14" t="s">
         <v>31</v>
       </c>
@@ -16448,7 +16438,7 @@
         <v>70.87</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="14" t="s">
         <v>74</v>
       </c>
@@ -16474,7 +16464,7 @@
         <v>112.74</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="14" t="s">
         <v>125</v>
       </c>
@@ -16500,7 +16490,7 @@
         <v>86.08</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="14" t="s">
         <v>78</v>
       </c>
@@ -16526,7 +16516,7 @@
         <v>75.34</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="14" t="s">
         <v>88</v>
       </c>
@@ -16552,7 +16542,7 @@
         <v>83.5</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="14" t="s">
         <v>110</v>
       </c>
@@ -16578,7 +16568,7 @@
         <v>127.08</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="14" t="s">
         <v>52</v>
       </c>
@@ -16604,7 +16594,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="14" t="s">
         <v>126</v>
       </c>
@@ -16630,7 +16620,7 @@
         <v>73.59</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="14" t="s">
         <v>44</v>
       </c>
@@ -16656,7 +16646,7 @@
         <v>79.260000000000005</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="14" t="s">
         <v>117</v>
       </c>
@@ -16682,7 +16672,7 @@
         <v>113.19</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="14" t="s">
         <v>195</v>
       </c>
@@ -16708,7 +16698,7 @@
         <v>95.09</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="14" t="s">
         <v>76</v>
       </c>
@@ -16734,7 +16724,7 @@
         <v>86.74</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="14" t="s">
         <v>23</v>
       </c>
@@ -16760,7 +16750,7 @@
         <v>100.28</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="14" t="s">
         <v>124</v>
       </c>
@@ -16786,7 +16776,7 @@
         <v>120.39</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="14" t="s">
         <v>6</v>
       </c>
@@ -16812,7 +16802,7 @@
         <v>95.65</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="14" t="s">
         <v>198</v>
       </c>
@@ -16838,7 +16828,7 @@
         <v>116.7</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="14" t="s">
         <v>90</v>
       </c>
@@ -16864,7 +16854,7 @@
         <v>101.22</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="14" t="s">
         <v>79</v>
       </c>
@@ -16890,7 +16880,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="14" t="s">
         <v>55</v>
       </c>
@@ -16916,7 +16906,7 @@
         <v>48.33</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="14" t="s">
         <v>128</v>
       </c>
@@ -16942,7 +16932,7 @@
         <v>84.58</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="14" t="s">
         <v>24</v>
       </c>
